--- a/docs/all-profiles.xlsx
+++ b/docs/all-profiles.xlsx
@@ -6099,17 +6099,17 @@
   <dimension ref="A1:AK793"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="34.48046875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="70.86328125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="52.90234375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="21.19140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="41.37890625" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="5.9296875" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="4.47265625" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="4.87890625" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="14.2734375" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="32.87890625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="67.57421875" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="50.44921875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="20.2109375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="39.4609375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="5.65234375" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.265625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="4.65234375" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="13.609375" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="12.75390625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="12.1640625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -6118,21 +6118,21 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="7.953125" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="36.22265625" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="15.4609375" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="15.86328125" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="17.203125" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="16.625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="116.9453125" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="76.33984375" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="5.52734375" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="21.87890625" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="38.34375" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="15.06640625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="12.421875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="33.03515625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="9.28515625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="7.58203125" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="34.54296875" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="14.7421875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="15.12890625" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.40625" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="15.85546875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="111.515625" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="72.796875" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="5.2734375" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="20.86328125" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="36.56640625" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="14.3671875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="11.84375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="31.50390625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="8.85546875" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
   </cols>
   <sheetData>
@@ -26194,7 +26194,7 @@
         <v>74</v>
       </c>
       <c r="H192" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="I192" t="s" s="2">
         <v>82</v>
@@ -38221,7 +38221,7 @@
         <v>74</v>
       </c>
       <c r="H307" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="I307" t="s" s="2">
         <v>82</v>

--- a/docs/all-profiles.xlsx
+++ b/docs/all-profiles.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26408" uniqueCount="1650">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26387" uniqueCount="1641">
   <si>
     <t>Property</t>
   </si>
@@ -343,7 +343,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -489,7 +489,7 @@
     <t>example</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/appointment-cancellation-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/appointment-cancellation-reason|4.0.1</t>
   </si>
   <si>
     <t>Appointment.serviceCategory</t>
@@ -832,7 +832,7 @@
     <t>The Reason for the appointment to take place.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/encounter-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/encounter-reason|4.0.1</t>
   </si>
   <si>
     <t>Appointment.reasonReference</t>
@@ -892,7 +892,7 @@
     <t>Aa resource (or, for logical models, the URI of the logical model).</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/resource-types</t>
+    <t>http://hl7.org/fhir/ValueSet/resource-types|4.0.1</t>
   </si>
   <si>
     <t>Reference.type</t>
@@ -1038,7 +1038,7 @@
     <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type|4.0.1</t>
   </si>
   <si>
     <t>Identifier.type</t>
@@ -1102,7 +1102,7 @@
     <t>Appointment.supportingInformation.identifier.assigner</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization)
+    <t xml:space="preserve">Reference(Organization|4.0.1)
 </t>
   </si>
   <si>
@@ -1213,7 +1213,7 @@
     <t>Appointment.slot</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Slot)
+    <t xml:space="preserve">Reference(Slot|4.0.1)
 </t>
   </si>
   <si>
@@ -1678,7 +1678,7 @@
     <t>Coding of the severity with a terminology is preferred, where possible.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/condition-severity</t>
+    <t>http://hl7.org/fhir/ValueSet/condition-severity|4.0.1</t>
   </si>
   <si>
     <t>Condition.code</t>
@@ -1748,7 +1748,7 @@
     <t>Codes describing anatomical locations. May include laterality.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/body-site</t>
+    <t>http://hl7.org/fhir/ValueSet/body-site|4.0.1</t>
   </si>
   <si>
     <t>Condition.subject</t>
@@ -1962,7 +1962,7 @@
     <t>Condition.encounter</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Encounter)
+    <t xml:space="preserve">Reference(Encounter|4.0.1)
 </t>
   </si>
   <si>
@@ -2019,7 +2019,7 @@
     <t>Condition.recorder</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|PractitionerRole|Patient|RelatedPerson)
+    <t xml:space="preserve">Reference(Practitioner|4.0.1|PractitionerRole|4.0.1|Patient|4.0.1|RelatedPerson|4.0.1)
 </t>
   </si>
   <si>
@@ -2072,7 +2072,7 @@
     <t>Codes describing condition stages (e.g. Cancer stages).</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/condition-stage</t>
+    <t>http://hl7.org/fhir/ValueSet/condition-stage|4.0.1</t>
   </si>
   <si>
     <t xml:space="preserve">con-1
@@ -2082,7 +2082,7 @@
     <t>Condition.stage.assessment</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(ClinicalImpression|DiagnosticReport|Observation)
+    <t xml:space="preserve">Reference(ClinicalImpression|4.0.1|DiagnosticReport|4.0.1|Observation|4.0.1)
 </t>
   </si>
   <si>
@@ -2104,7 +2104,7 @@
     <t>Codes describing the kind of condition staging (e.g. clinical or pathological).</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/condition-stage-type</t>
+    <t>http://hl7.org/fhir/ValueSet/condition-stage-type|4.0.1</t>
   </si>
   <si>
     <t>Condition.evidence</t>
@@ -2144,7 +2144,7 @@
     <t>Codes that describe the manifestation or symptoms of a condition.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/manifestation-or-symptom</t>
+    <t>http://hl7.org/fhir/ValueSet/manifestation-or-symptom|4.0.1</t>
   </si>
   <si>
     <t xml:space="preserve">con-2
@@ -2154,7 +2154,7 @@
     <t>Condition.evidence.detail</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -2186,7 +2186,7 @@
     <t>Condition.note.author[x]</t>
   </si>
   <si>
-    <t>Reference(Practitioner|Patient|RelatedPerson|Organization)
+    <t>Reference(Practitioner|4.0.1|Patient|4.0.1|RelatedPerson|4.0.1|Organization|4.0.1)
 string</t>
   </si>
   <si>
@@ -2865,7 +2865,7 @@
     <t>Composition.attester.party</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient|RelatedPerson|Practitioner|PractitionerRole|Organization)
+    <t xml:space="preserve">Reference(Patient|4.0.1|RelatedPerson|4.0.1|Practitioner|4.0.1|PractitionerRole|4.0.1|Organization|4.0.1)
 </t>
   </si>
   <si>
@@ -4104,13 +4104,13 @@
     <t>Classification of a section of a composition/document.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/doc-section-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/doc-section-codes|4.0.1</t>
   </si>
   <si>
     <t>Composition.section.author</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|PractitionerRole|Device|Patient|RelatedPerson|Organization)
+    <t xml:space="preserve">Reference(Practitioner|4.0.1|PractitionerRole|4.0.1|Device|4.0.1|Patient|4.0.1|RelatedPerson|4.0.1|Organization|4.0.1)
 </t>
   </si>
   <si>
@@ -4187,7 +4187,7 @@
     <t>What order applies to the items in the entry.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/list-order</t>
+    <t>http://hl7.org/fhir/ValueSet/list-order|4.0.1</t>
   </si>
   <si>
     <t>Composition.section.entry</t>
@@ -4246,7 +4246,7 @@
     <t>If a section is empty, why it is empty.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/list-empty-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/list-empty-reason|4.0.1</t>
   </si>
   <si>
     <t>Composition.section.section</t>
@@ -4287,7 +4287,7 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}prr-1:orderDetail SHALL only be present if code is present {orderDetail.empty() or code.exists()}</t>
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}prr-1:orderDetail SHALL only be present if code is present {orderDetail.empty() or code.exists()}</t>
   </si>
   <si>
     <t>ServiceRequest.id</t>
@@ -4314,9 +4314,6 @@
     <t>ServiceRequest.modifierExtension</t>
   </si>
   <si>
-    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](extensibility.html#modifierExtension).</t>
-  </si>
-  <si>
     <t>ServiceRequest.identifier</t>
   </si>
   <si>
@@ -4332,7 +4329,7 @@
     <t>ServiceRequest.instantiatesCanonical</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(ActivityDefinition|PlanDefinition)
+    <t xml:space="preserve">canonical(ActivityDefinition|4.0.1|PlanDefinition|4.0.1)
 </t>
   </si>
   <si>
@@ -4342,7 +4339,7 @@
     <t>The URL pointing to a FHIR-defined protocol, guideline, orderset or other definition that is adhered to in whole or in part by this ServiceRequest.</t>
   </si>
   <si>
-    <t>Note: This is a business identifier, not a resource identifier (see [discussion](resource.html#identifiers)).  It is best practice for the identifier to only appear on a single resource instance, however business practices may occasionally dictate that multiple resource instances with the same identifier can exist - possibly even with different resource types.  For example, multiple Patient and a Person resource instance might share the same social insurance number.</t>
+    <t>Note: This is a business identifier, not a resource identifier (see [discussion](http://hl7.org/fhir/R4/resource.html#identifiers)).  It is best practice for the identifier to only appear on a single resource instance, however business practices may occasionally dictate that multiple resource instances with the same identifier can exist - possibly even with different resource types.  For example, multiple Patient and a Person resource instance might share the same social insurance number.</t>
   </si>
   <si>
     <t>ServiceRequest.instantiatesUri</t>
@@ -4364,7 +4361,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(CarePlan|ServiceRequest|MedicationRequest)
+    <t xml:space="preserve">Reference(CarePlan|4.0.1|ServiceRequest|4.0.1|MedicationRequest|4.0.1)
 </t>
   </si>
   <si>
@@ -4372,13 +4369,6 @@
   </si>
   <si>
     <t>Plan/proposal/order fulfilled by this request.</t>
-  </si>
-  <si>
-    <t>References SHALL be a reference to an actual FHIR resource, and SHALL be resolveable (allowing for access control, temporary unavailability, etc.). Resolution can be either by retrieval from the URL, or, where applicable by resource type, by treating an absolute reference as a canonical URL and looking it up in a local registry/repository.</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ref-1:SHALL have a contained resource if a local reference is provided {reference.startsWith('#').not() or (reference.substring(1).trace('url') in %rootResource.contained.id.trace('ids'))}</t>
   </si>
   <si>
     <t>ServiceRequest.replaces</t>
@@ -4388,7 +4378,7 @@
 priorrenewed order</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(ServiceRequest)
+    <t xml:space="preserve">Reference(ServiceRequest|4.0.1)
 </t>
   </si>
   <si>
@@ -4426,10 +4416,7 @@
     <t>The status of the order.</t>
   </si>
   <si>
-    <t>The status is generally fully in the control of the requester - they determine whether the order is draft or active and, after it has been activated, competed, cancelled or suspended. States relating to the activities of the performer are reflected on either the corresponding event (see [Event Pattern](event.html) for general discussion) or using the [Task](task.html) resource.</t>
-  </si>
-  <si>
-    <t>The status of a service order.</t>
+    <t>The status is generally fully in the control of the requester - they determine whether the order is draft or active and, after it has been activated, competed, cancelled or suspended. States relating to the activities of the performer are reflected on either the corresponding event (see [Event Pattern](http://hl7.org/fhir/R4/event.html) for general discussion) or using the [Task](http://hl7.org/fhir/R4/task.html) resource.</t>
   </si>
   <si>
     <t>http://www.saude.gov.br/fhir/r4/ValueSet/BRStatusRequisicaoRegulacaoAssistencial</t>
@@ -4447,9 +4434,6 @@
     <t>This element is labeled as a modifier because the intent alters when and how the resource is actually applicable.</t>
   </si>
   <si>
-    <t>The kind of service request.</t>
-  </si>
-  <si>
     <t>http://www.saude.gov.br/fhir/r4/ValueSet/BRIntencaoRegulacao</t>
   </si>
   <si>
@@ -4487,9 +4471,6 @@
   </si>
   <si>
     <t>ServiceRequest.category.coding.code</t>
-  </si>
-  <si>
-    <t>Note that FHIR strings SHALL NOT exceed 1MB in size</t>
   </si>
   <si>
     <t>ServiceRequest.category.coding.display</t>
@@ -4599,11 +4580,11 @@
     <t>Codified order entry details which are based on order context.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/servicerequest-orderdetail</t>
-  </si>
-  <si>
-    <t>ele-1
-prr-1</t>
+    <t>http://hl7.org/fhir/ValueSet/servicerequest-orderdetail|4.0.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">prr-1
+</t>
   </si>
   <si>
     <t>ServiceRequest.quantity[x]</t>
@@ -4637,10 +4618,6 @@
     <t>ServiceRequest.subject.reference</t>
   </si>
   <si>
-    <t>ele-1
-ref-1</t>
-  </si>
-  <si>
     <t>ServiceRequest.subject.type</t>
   </si>
   <si>
@@ -4665,18 +4642,7 @@
     <t>ServiceRequest.subject.identifier.value</t>
   </si>
   <si>
-    <t>If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
-  </si>
-  <si>
     <t>ServiceRequest.subject.identifier.period</t>
-  </si>
-  <si>
-    <t>A Period specifies a range of time; the context of use will specify whether the entire range applies (e.g. "the patient was an inpatient of the hospital for this time range") or one value from the range applies (e.g. "give to the patient between these two times").
-Period is not used for a duration (a measure of elapsed time). See [Duration](datatypes.html#Duration).</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-per-1:If present, start SHALL have a lower value than end {start.hasValue().not() or end.hasValue().not() or (start &lt;= end)}</t>
   </si>
   <si>
     <t>ServiceRequest.subject.identifier.assigner</t>
@@ -4714,6 +4680,12 @@
     <t>ServiceRequest.occurrence[x].id</t>
   </si>
   <si>
+    <t>xml:id (or equivalent in JSON)</t>
+  </si>
+  <si>
+    <t>unique id for the element within a resource (for internal references)</t>
+  </si>
+  <si>
     <t>ServiceRequest.occurrence[x].extension</t>
   </si>
   <si>
@@ -4721,6 +4693,9 @@
   </si>
   <si>
     <t>Primitive value for dateTime</t>
+  </si>
+  <si>
+    <t>The actual value</t>
   </si>
   <si>
     <t>dateTime.value</t>
@@ -4742,7 +4717,7 @@
     <t>A coded concept identifying the pre-condition that should hold prior to performing a procedure.  For example "pain", "on flare-up", etc.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/medication-as-needed-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/medication-as-needed-reason|4.0.1</t>
   </si>
   <si>
     <t>ServiceRequest.authoredOn</t>
@@ -4875,7 +4850,7 @@
     <t>The desired performer for doing the requested service.  For example, the surgeon, dermatopathologist, endoscopist, etc.</t>
   </si>
   <si>
-    <t>If multiple performers are present, it is interpreted as a list of *alternative* performers without any preference regardless of order.  If order of preference is needed use the [request-performerOrder extension](extension-request-performerorder.html).  Use CareTeam to represent a group of performers (for example, Practitioner A *and* Practitioner B).</t>
+    <t>If multiple performers are present, it is interpreted as a list of *alternative* performers without any preference regardless of order.  If order of preference is needed use the [request-performerOrder extension](http://hl7.org/fhir/R4/extension-request-performerorder.html).  Use CareTeam to represent a group of performers (for example, Practitioner A *and* Practitioner B).</t>
   </si>
   <si>
     <t>ServiceRequest.performer.id</t>
@@ -4929,9 +4904,6 @@
     <t>The preferred location(s) where the procedure should actually happen in coded or free text form. E.g. at home or nursing day care center.</t>
   </si>
   <si>
-    <t>Not all terminology uses fit this general pattern. In some cases, models should not use CodeableConcept and use Coding directly and provide their own structure for managing text, codings, translations and the relationship between elements and pre- and post-coordination.</t>
-  </si>
-  <si>
     <t>A location type where services are delivered.</t>
   </si>
   <si>
@@ -4941,7 +4913,7 @@
     <t>ServiceRequest.locationReference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Location)
+    <t xml:space="preserve">Reference(Location|4.0.1)
 </t>
   </si>
   <si>
@@ -4957,13 +4929,13 @@
     <t>An explanation or justification for why this service is being requested in coded or textual form.   This is often for billing purposes.  May relate to the resources referred to in `supportingInfo`.</t>
   </si>
   <si>
-    <t>This element represents why the referral is being made and may be used to decide how the service will be performed, or even if it will be performed at all.   Use `CodeableConcept.text` element if the data is free (uncoded) text as shown in the [CT Scan example](servicerequest-example-di.html).</t>
+    <t>This element represents why the referral is being made and may be used to decide how the service will be performed, or even if it will be performed at all.   Use `CodeableConcept.text` element if the data is free (uncoded) text as shown in the [CT Scan example](http://hl7.org/fhir/R4/servicerequest-example-di.html).</t>
   </si>
   <si>
     <t>Diagnosis or problem codes justifying the reason for requesting the service investigation.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/procedure-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/procedure-reason|4.0.1</t>
   </si>
   <si>
     <t>ServiceRequest.reasonReference</t>
@@ -4972,7 +4944,7 @@
     <t>Indicates another resource that provides a justification for why this service is being requested.   May relate to the resources referred to in `supportingInfo`.</t>
   </si>
   <si>
-    <t>This element represents why the referral is being made and may be used to decide how the service will be performed, or even if it will be performed at all.    To be as specific as possible,  a reference to  *Observation* or *Condition* should be used if available.  Otherwise when referencing  *DiagnosticReport*  it should contain a finding  in `DiagnosticReport.conclusion` and/or `DiagnosticReport.conclusionCode`.   When using a reference to *DocumentReference*, the target document should contain clear findings language providing the relevant reason for this service request.  Use  the CodeableConcept text element in `ServiceRequest.reasonCode` if the data is free (uncoded) text as shown in the [CT Scan example](servicerequest-example-di.html).</t>
+    <t>This element represents why the referral is being made and may be used to decide how the service will be performed, or even if it will be performed at all.    To be as specific as possible,  a reference to  *Observation* or *Condition* should be used if available.  Otherwise when referencing  *DiagnosticReport*  it should contain a finding  in `DiagnosticReport.conclusion` and/or `DiagnosticReport.conclusionCode`.   When using a reference to *DocumentReference*, the target document should contain clear findings language providing the relevant reason for this service request.  Use  the CodeableConcept text element in `ServiceRequest.reasonCode` if the data is free (uncoded) text as shown in the [CT Scan example](http://hl7.org/fhir/R4/servicerequest-example-di.html).</t>
   </si>
   <si>
     <t>ServiceRequest.reasonReference.id</t>
@@ -4996,7 +4968,7 @@
     <t>ServiceRequest.insurance</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Coverage|ClaimResponse)
+    <t xml:space="preserve">Reference(Coverage|4.0.1|ClaimResponse|4.0.1)
 </t>
   </si>
   <si>
@@ -5025,7 +4997,7 @@
     <t>ServiceRequest.specimen</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Specimen)
+    <t xml:space="preserve">Reference(Specimen|4.0.1)
 </t>
   </si>
   <si>
@@ -5035,7 +5007,7 @@
     <t>One or more specimens that the laboratory procedure will use.</t>
   </si>
   <si>
-    <t>Many diagnostic procedures need a specimen, but the request itself is not actually about the specimen. This element is for when the diagnostic is requested on already existing specimens and the request points to the specimen it applies to.    Conversely, if the request is entered first with an unknown specimen, then the [Specimen](specimen.html) resource points to the ServiceRequest.</t>
+    <t>Many diagnostic procedures need a specimen, but the request itself is not actually about the specimen. This element is for when the diagnostic is requested on already existing specimens and the request points to the specimen it applies to.    Conversely, if the request is entered first with an unknown specimen, then the [Specimen](http://hl7.org/fhir/R4/specimen.html) resource points to the ServiceRequest.</t>
   </si>
   <si>
     <t>ServiceRequest.bodySite</t>
@@ -5051,7 +5023,7 @@
     <t>Anatomic location where the procedure should be performed. This is the target site.</t>
   </si>
   <si>
-    <t>Only used if not implicit in the code found in ServiceRequest.code.  If the use case requires BodySite to be handled as a separate resource instead of an inline coded element (e.g. to identify and track separately)  then use the standard extension [procedure-targetBodyStructure](extension-procedure-targetbodystructure.html).</t>
+    <t>Only used if not implicit in the code found in ServiceRequest.code.  If the use case requires BodySite to be handled as a separate resource instead of an inline coded element (e.g. to identify and track separately)  then use the standard extension [procedure-targetBodyStructure](http://hl7.org/fhir/R4/extension-procedure-targetbodystructure.html).</t>
   </si>
   <si>
     <t>Knowing where the procedure is performed is important for tracking if multiple sites are possible.</t>
@@ -5063,9 +5035,6 @@
     <t>Any other notes and comments made about the service request. For example, internal billing notes.</t>
   </si>
   <si>
-    <t>For systems that do not have structured annotations, they can simply communicate a single annotation with no author or time.  This element may need to be included in narrative because of the potential for modifying information.  *Annotations SHOULD NOT* be used to communicate "modifying" information that could be computable. (This is a SHOULD because enforcing user behavior is nearly impossible).</t>
-  </si>
-  <si>
     <t>ServiceRequest.patientInstruction</t>
   </si>
   <si>
@@ -5078,7 +5047,7 @@
     <t>ServiceRequest.relevantHistory</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Provenance)
+    <t xml:space="preserve">Reference(Provenance|4.0.1)
 </t>
   </si>
   <si>
@@ -76267,7 +76236,7 @@
         <v>82</v>
       </c>
       <c r="L669" t="s" s="2">
-        <v>159</v>
+        <v>83</v>
       </c>
       <c r="M669" t="s" s="2">
         <v>84</v>
@@ -76438,7 +76407,7 @@
         <v>81</v>
       </c>
       <c r="AJ670" t="s" s="2">
-        <v>727</v>
+        <v>73</v>
       </c>
       <c r="AK670" t="s" s="2">
         <v>93</v>
@@ -76543,7 +76512,7 @@
         <v>81</v>
       </c>
       <c r="AJ671" t="s" s="2">
-        <v>727</v>
+        <v>73</v>
       </c>
       <c r="AK671" t="s" s="2">
         <v>93</v>
@@ -76648,7 +76617,7 @@
         <v>81</v>
       </c>
       <c r="AJ672" t="s" s="2">
-        <v>727</v>
+        <v>73</v>
       </c>
       <c r="AK672" t="s" s="2">
         <v>93</v>
@@ -76753,7 +76722,7 @@
         <v>81</v>
       </c>
       <c r="AJ673" t="s" s="2">
-        <v>727</v>
+        <v>73</v>
       </c>
       <c r="AK673" t="s" s="2">
         <v>93</v>
@@ -76942,16 +76911,16 @@
         <v>73</v>
       </c>
       <c r="AC675" t="s" s="2">
-        <v>165</v>
+        <v>73</v>
       </c>
       <c r="AD675" t="s" s="2">
-        <v>166</v>
+        <v>73</v>
       </c>
       <c r="AE675" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AF675" t="s" s="2">
-        <v>167</v>
+        <v>73</v>
       </c>
       <c r="AG675" t="s" s="2">
         <v>129</v>
@@ -76963,7 +76932,7 @@
         <v>75</v>
       </c>
       <c r="AJ675" t="s" s="2">
-        <v>727</v>
+        <v>73</v>
       </c>
       <c r="AK675" t="s" s="2">
         <v>130</v>
@@ -77012,7 +76981,7 @@
         <v>128</v>
       </c>
       <c r="P676" t="s" s="2">
-        <v>1400</v>
+        <v>134</v>
       </c>
       <c r="Q676" t="s" s="2">
         <v>73</v>
@@ -77049,16 +77018,16 @@
         <v>73</v>
       </c>
       <c r="AC676" t="s" s="2">
-        <v>165</v>
+        <v>73</v>
       </c>
       <c r="AD676" t="s" s="2">
-        <v>166</v>
+        <v>73</v>
       </c>
       <c r="AE676" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AF676" t="s" s="2">
-        <v>167</v>
+        <v>73</v>
       </c>
       <c r="AG676" t="s" s="2">
         <v>135</v>
@@ -77070,7 +77039,7 @@
         <v>75</v>
       </c>
       <c r="AJ676" t="s" s="2">
-        <v>727</v>
+        <v>73</v>
       </c>
       <c r="AK676" t="s" s="2">
         <v>130</v>
@@ -77081,10 +77050,10 @@
         <v>1383</v>
       </c>
       <c r="B677" t="s" s="2">
-        <v>1401</v>
+        <v>1400</v>
       </c>
       <c r="C677" t="s" s="2">
-        <v>1401</v>
+        <v>1400</v>
       </c>
       <c r="D677" s="2"/>
       <c r="E677" t="s" s="2">
@@ -77110,13 +77079,13 @@
         <v>137</v>
       </c>
       <c r="M677" t="s" s="2">
+        <v>1401</v>
+      </c>
+      <c r="N677" t="s" s="2">
         <v>1402</v>
       </c>
-      <c r="N677" t="s" s="2">
+      <c r="O677" t="s" s="2">
         <v>1403</v>
-      </c>
-      <c r="O677" t="s" s="2">
-        <v>1404</v>
       </c>
       <c r="P677" s="2"/>
       <c r="Q677" t="s" s="2">
@@ -77166,7 +77135,7 @@
         <v>73</v>
       </c>
       <c r="AG677" t="s" s="2">
-        <v>1401</v>
+        <v>1400</v>
       </c>
       <c r="AH677" t="s" s="2">
         <v>74</v>
@@ -77175,7 +77144,7 @@
         <v>75</v>
       </c>
       <c r="AJ677" t="s" s="2">
-        <v>727</v>
+        <v>73</v>
       </c>
       <c r="AK677" t="s" s="2">
         <v>93</v>
@@ -77186,10 +77155,10 @@
         <v>1383</v>
       </c>
       <c r="B678" t="s" s="2">
-        <v>1405</v>
+        <v>1404</v>
       </c>
       <c r="C678" t="s" s="2">
-        <v>1405</v>
+        <v>1404</v>
       </c>
       <c r="D678" s="2"/>
       <c r="E678" t="s" s="2">
@@ -77212,16 +77181,16 @@
         <v>82</v>
       </c>
       <c r="L678" t="s" s="2">
+        <v>1405</v>
+      </c>
+      <c r="M678" t="s" s="2">
         <v>1406</v>
       </c>
-      <c r="M678" t="s" s="2">
+      <c r="N678" t="s" s="2">
         <v>1407</v>
       </c>
-      <c r="N678" t="s" s="2">
+      <c r="O678" t="s" s="2">
         <v>1408</v>
-      </c>
-      <c r="O678" t="s" s="2">
-        <v>1409</v>
       </c>
       <c r="P678" s="2"/>
       <c r="Q678" t="s" s="2">
@@ -77271,7 +77240,7 @@
         <v>73</v>
       </c>
       <c r="AG678" t="s" s="2">
-        <v>1405</v>
+        <v>1404</v>
       </c>
       <c r="AH678" t="s" s="2">
         <v>74</v>
@@ -77280,7 +77249,7 @@
         <v>75</v>
       </c>
       <c r="AJ678" t="s" s="2">
-        <v>727</v>
+        <v>73</v>
       </c>
       <c r="AK678" t="s" s="2">
         <v>93</v>
@@ -77291,10 +77260,10 @@
         <v>1383</v>
       </c>
       <c r="B679" t="s" s="2">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="C679" t="s" s="2">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="D679" s="2"/>
       <c r="E679" t="s" s="2">
@@ -77320,13 +77289,13 @@
         <v>95</v>
       </c>
       <c r="M679" t="s" s="2">
+        <v>1410</v>
+      </c>
+      <c r="N679" t="s" s="2">
         <v>1411</v>
       </c>
-      <c r="N679" t="s" s="2">
+      <c r="O679" t="s" s="2">
         <v>1412</v>
-      </c>
-      <c r="O679" t="s" s="2">
-        <v>1413</v>
       </c>
       <c r="P679" s="2"/>
       <c r="Q679" t="s" s="2">
@@ -77376,7 +77345,7 @@
         <v>73</v>
       </c>
       <c r="AG679" t="s" s="2">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="AH679" t="s" s="2">
         <v>74</v>
@@ -77385,7 +77354,7 @@
         <v>75</v>
       </c>
       <c r="AJ679" t="s" s="2">
-        <v>727</v>
+        <v>73</v>
       </c>
       <c r="AK679" t="s" s="2">
         <v>93</v>
@@ -77396,14 +77365,14 @@
         <v>1383</v>
       </c>
       <c r="B680" t="s" s="2">
-        <v>1414</v>
+        <v>1413</v>
       </c>
       <c r="C680" t="s" s="2">
-        <v>1414</v>
+        <v>1413</v>
       </c>
       <c r="D680" s="2"/>
       <c r="E680" t="s" s="2">
-        <v>1415</v>
+        <v>1414</v>
       </c>
       <c r="F680" s="2"/>
       <c r="G680" t="s" s="2">
@@ -77422,17 +77391,15 @@
         <v>82</v>
       </c>
       <c r="L680" t="s" s="2">
+        <v>1415</v>
+      </c>
+      <c r="M680" t="s" s="2">
         <v>1416</v>
       </c>
-      <c r="M680" t="s" s="2">
+      <c r="N680" t="s" s="2">
         <v>1417</v>
       </c>
-      <c r="N680" t="s" s="2">
-        <v>1418</v>
-      </c>
-      <c r="O680" t="s" s="2">
-        <v>1419</v>
-      </c>
+      <c r="O680" s="2"/>
       <c r="P680" s="2"/>
       <c r="Q680" t="s" s="2">
         <v>73</v>
@@ -77481,7 +77448,7 @@
         <v>73</v>
       </c>
       <c r="AG680" t="s" s="2">
-        <v>1414</v>
+        <v>1413</v>
       </c>
       <c r="AH680" t="s" s="2">
         <v>74</v>
@@ -77490,10 +77457,10 @@
         <v>75</v>
       </c>
       <c r="AJ680" t="s" s="2">
-        <v>727</v>
+        <v>73</v>
       </c>
       <c r="AK680" t="s" s="2">
-        <v>1420</v>
+        <v>93</v>
       </c>
     </row>
     <row r="681">
@@ -77501,14 +77468,14 @@
         <v>1383</v>
       </c>
       <c r="B681" t="s" s="2">
-        <v>1421</v>
+        <v>1418</v>
       </c>
       <c r="C681" t="s" s="2">
-        <v>1421</v>
+        <v>1418</v>
       </c>
       <c r="D681" s="2"/>
       <c r="E681" t="s" s="2">
-        <v>1422</v>
+        <v>1419</v>
       </c>
       <c r="F681" s="2"/>
       <c r="G681" t="s" s="2">
@@ -77527,17 +77494,15 @@
         <v>82</v>
       </c>
       <c r="L681" t="s" s="2">
-        <v>1423</v>
+        <v>1420</v>
       </c>
       <c r="M681" t="s" s="2">
-        <v>1424</v>
+        <v>1421</v>
       </c>
       <c r="N681" t="s" s="2">
-        <v>1425</v>
-      </c>
-      <c r="O681" t="s" s="2">
-        <v>1419</v>
-      </c>
+        <v>1422</v>
+      </c>
+      <c r="O681" s="2"/>
       <c r="P681" s="2"/>
       <c r="Q681" t="s" s="2">
         <v>73</v>
@@ -77586,7 +77551,7 @@
         <v>73</v>
       </c>
       <c r="AG681" t="s" s="2">
-        <v>1421</v>
+        <v>1418</v>
       </c>
       <c r="AH681" t="s" s="2">
         <v>74</v>
@@ -77595,10 +77560,10 @@
         <v>75</v>
       </c>
       <c r="AJ681" t="s" s="2">
-        <v>727</v>
+        <v>73</v>
       </c>
       <c r="AK681" t="s" s="2">
-        <v>1420</v>
+        <v>93</v>
       </c>
     </row>
     <row r="682">
@@ -77606,14 +77571,14 @@
         <v>1383</v>
       </c>
       <c r="B682" t="s" s="2">
-        <v>1426</v>
+        <v>1423</v>
       </c>
       <c r="C682" t="s" s="2">
-        <v>1426</v>
+        <v>1423</v>
       </c>
       <c r="D682" s="2"/>
       <c r="E682" t="s" s="2">
-        <v>1427</v>
+        <v>1424</v>
       </c>
       <c r="F682" s="2"/>
       <c r="G682" t="s" s="2">
@@ -77635,16 +77600,16 @@
         <v>137</v>
       </c>
       <c r="M682" t="s" s="2">
+        <v>1425</v>
+      </c>
+      <c r="N682" t="s" s="2">
+        <v>1426</v>
+      </c>
+      <c r="O682" t="s" s="2">
+        <v>1427</v>
+      </c>
+      <c r="P682" t="s" s="2">
         <v>1428</v>
-      </c>
-      <c r="N682" t="s" s="2">
-        <v>1429</v>
-      </c>
-      <c r="O682" t="s" s="2">
-        <v>1430</v>
-      </c>
-      <c r="P682" t="s" s="2">
-        <v>1431</v>
       </c>
       <c r="Q682" t="s" s="2">
         <v>73</v>
@@ -77693,7 +77658,7 @@
         <v>73</v>
       </c>
       <c r="AG682" t="s" s="2">
-        <v>1426</v>
+        <v>1423</v>
       </c>
       <c r="AH682" t="s" s="2">
         <v>74</v>
@@ -77702,7 +77667,7 @@
         <v>81</v>
       </c>
       <c r="AJ682" t="s" s="2">
-        <v>727</v>
+        <v>73</v>
       </c>
       <c r="AK682" t="s" s="2">
         <v>93</v>
@@ -77713,10 +77678,10 @@
         <v>1383</v>
       </c>
       <c r="B683" t="s" s="2">
-        <v>1432</v>
+        <v>1429</v>
       </c>
       <c r="C683" t="s" s="2">
-        <v>1432</v>
+        <v>1429</v>
       </c>
       <c r="D683" s="2"/>
       <c r="E683" t="s" s="2">
@@ -77742,13 +77707,13 @@
         <v>101</v>
       </c>
       <c r="M683" t="s" s="2">
-        <v>1433</v>
+        <v>1430</v>
       </c>
       <c r="N683" t="s" s="2">
-        <v>1434</v>
+        <v>1431</v>
       </c>
       <c r="O683" t="s" s="2">
-        <v>1435</v>
+        <v>1432</v>
       </c>
       <c r="P683" s="2"/>
       <c r="Q683" t="s" s="2">
@@ -77776,11 +77741,9 @@
       <c r="Y683" t="s" s="2">
         <v>144</v>
       </c>
-      <c r="Z683" t="s" s="2">
-        <v>1436</v>
-      </c>
+      <c r="Z683" s="2"/>
       <c r="AA683" t="s" s="2">
-        <v>1437</v>
+        <v>1433</v>
       </c>
       <c r="AB683" t="s" s="2">
         <v>73</v>
@@ -77798,7 +77761,7 @@
         <v>73</v>
       </c>
       <c r="AG683" t="s" s="2">
-        <v>1432</v>
+        <v>1429</v>
       </c>
       <c r="AH683" t="s" s="2">
         <v>81</v>
@@ -77807,7 +77770,7 @@
         <v>81</v>
       </c>
       <c r="AJ683" t="s" s="2">
-        <v>727</v>
+        <v>73</v>
       </c>
       <c r="AK683" t="s" s="2">
         <v>93</v>
@@ -77818,10 +77781,10 @@
         <v>1383</v>
       </c>
       <c r="B684" t="s" s="2">
-        <v>1438</v>
+        <v>1434</v>
       </c>
       <c r="C684" t="s" s="2">
-        <v>1438</v>
+        <v>1434</v>
       </c>
       <c r="D684" s="2"/>
       <c r="E684" t="s" s="2">
@@ -77847,13 +77810,13 @@
         <v>101</v>
       </c>
       <c r="M684" t="s" s="2">
-        <v>1439</v>
+        <v>1435</v>
       </c>
       <c r="N684" t="s" s="2">
-        <v>1440</v>
+        <v>1436</v>
       </c>
       <c r="O684" t="s" s="2">
-        <v>1441</v>
+        <v>1437</v>
       </c>
       <c r="P684" s="2"/>
       <c r="Q684" t="s" s="2">
@@ -77881,11 +77844,9 @@
       <c r="Y684" t="s" s="2">
         <v>144</v>
       </c>
-      <c r="Z684" t="s" s="2">
-        <v>1442</v>
-      </c>
+      <c r="Z684" s="2"/>
       <c r="AA684" t="s" s="2">
-        <v>1443</v>
+        <v>1438</v>
       </c>
       <c r="AB684" t="s" s="2">
         <v>73</v>
@@ -77903,7 +77864,7 @@
         <v>73</v>
       </c>
       <c r="AG684" t="s" s="2">
-        <v>1438</v>
+        <v>1434</v>
       </c>
       <c r="AH684" t="s" s="2">
         <v>81</v>
@@ -77912,7 +77873,7 @@
         <v>81</v>
       </c>
       <c r="AJ684" t="s" s="2">
-        <v>727</v>
+        <v>73</v>
       </c>
       <c r="AK684" t="s" s="2">
         <v>93</v>
@@ -77923,10 +77884,10 @@
         <v>1383</v>
       </c>
       <c r="B685" t="s" s="2">
-        <v>1444</v>
+        <v>1439</v>
       </c>
       <c r="C685" t="s" s="2">
-        <v>1444</v>
+        <v>1439</v>
       </c>
       <c r="D685" s="2"/>
       <c r="E685" t="s" s="2">
@@ -77955,13 +77916,13 @@
         <v>154</v>
       </c>
       <c r="N685" t="s" s="2">
-        <v>1445</v>
+        <v>1440</v>
       </c>
       <c r="O685" t="s" s="2">
-        <v>1446</v>
+        <v>1441</v>
       </c>
       <c r="P685" t="s" s="2">
-        <v>1447</v>
+        <v>1442</v>
       </c>
       <c r="Q685" t="s" s="2">
         <v>73</v>
@@ -78010,7 +77971,7 @@
         <v>73</v>
       </c>
       <c r="AG685" t="s" s="2">
-        <v>1444</v>
+        <v>1439</v>
       </c>
       <c r="AH685" t="s" s="2">
         <v>74</v>
@@ -78019,7 +77980,7 @@
         <v>75</v>
       </c>
       <c r="AJ685" t="s" s="2">
-        <v>727</v>
+        <v>73</v>
       </c>
       <c r="AK685" t="s" s="2">
         <v>93</v>
@@ -78030,10 +77991,10 @@
         <v>1383</v>
       </c>
       <c r="B686" t="s" s="2">
-        <v>1448</v>
+        <v>1443</v>
       </c>
       <c r="C686" t="s" s="2">
-        <v>1448</v>
+        <v>1443</v>
       </c>
       <c r="D686" s="2"/>
       <c r="E686" t="s" s="2">
@@ -78133,10 +78094,10 @@
         <v>1383</v>
       </c>
       <c r="B687" t="s" s="2">
-        <v>1449</v>
+        <v>1444</v>
       </c>
       <c r="C687" t="s" s="2">
-        <v>1449</v>
+        <v>1444</v>
       </c>
       <c r="D687" s="2"/>
       <c r="E687" t="s" s="2">
@@ -78227,7 +78188,7 @@
         <v>75</v>
       </c>
       <c r="AJ687" t="s" s="2">
-        <v>727</v>
+        <v>73</v>
       </c>
       <c r="AK687" t="s" s="2">
         <v>130</v>
@@ -78238,10 +78199,10 @@
         <v>1383</v>
       </c>
       <c r="B688" t="s" s="2">
-        <v>1450</v>
+        <v>1445</v>
       </c>
       <c r="C688" t="s" s="2">
-        <v>1450</v>
+        <v>1445</v>
       </c>
       <c r="D688" s="2"/>
       <c r="E688" t="s" s="2">
@@ -78334,7 +78295,7 @@
         <v>75</v>
       </c>
       <c r="AJ688" t="s" s="2">
-        <v>727</v>
+        <v>73</v>
       </c>
       <c r="AK688" t="s" s="2">
         <v>93</v>
@@ -78345,10 +78306,10 @@
         <v>1383</v>
       </c>
       <c r="B689" t="s" s="2">
-        <v>1451</v>
+        <v>1446</v>
       </c>
       <c r="C689" t="s" s="2">
-        <v>1451</v>
+        <v>1446</v>
       </c>
       <c r="D689" s="2"/>
       <c r="E689" t="s" s="2">
@@ -78448,10 +78409,10 @@
         <v>1383</v>
       </c>
       <c r="B690" t="s" s="2">
-        <v>1452</v>
+        <v>1447</v>
       </c>
       <c r="C690" t="s" s="2">
-        <v>1452</v>
+        <v>1447</v>
       </c>
       <c r="D690" s="2"/>
       <c r="E690" t="s" s="2">
@@ -78542,7 +78503,7 @@
         <v>75</v>
       </c>
       <c r="AJ690" t="s" s="2">
-        <v>727</v>
+        <v>73</v>
       </c>
       <c r="AK690" t="s" s="2">
         <v>130</v>
@@ -78553,10 +78514,10 @@
         <v>1383</v>
       </c>
       <c r="B691" t="s" s="2">
-        <v>1453</v>
+        <v>1448</v>
       </c>
       <c r="C691" t="s" s="2">
-        <v>1453</v>
+        <v>1448</v>
       </c>
       <c r="D691" s="2"/>
       <c r="E691" t="s" s="2">
@@ -78649,7 +78610,7 @@
         <v>81</v>
       </c>
       <c r="AJ691" t="s" s="2">
-        <v>727</v>
+        <v>73</v>
       </c>
       <c r="AK691" t="s" s="2">
         <v>93</v>
@@ -78660,10 +78621,10 @@
         <v>1383</v>
       </c>
       <c r="B692" t="s" s="2">
-        <v>1454</v>
+        <v>1449</v>
       </c>
       <c r="C692" t="s" s="2">
-        <v>1454</v>
+        <v>1449</v>
       </c>
       <c r="D692" s="2"/>
       <c r="E692" t="s" s="2">
@@ -78754,7 +78715,7 @@
         <v>81</v>
       </c>
       <c r="AJ692" t="s" s="2">
-        <v>727</v>
+        <v>73</v>
       </c>
       <c r="AK692" t="s" s="2">
         <v>93</v>
@@ -78765,10 +78726,10 @@
         <v>1383</v>
       </c>
       <c r="B693" t="s" s="2">
-        <v>1455</v>
+        <v>1450</v>
       </c>
       <c r="C693" t="s" s="2">
-        <v>1455</v>
+        <v>1450</v>
       </c>
       <c r="D693" s="2"/>
       <c r="E693" t="s" s="2">
@@ -78799,9 +78760,7 @@
       <c r="N693" t="s" s="2">
         <v>191</v>
       </c>
-      <c r="O693" t="s" s="2">
-        <v>1456</v>
-      </c>
+      <c r="O693" s="2"/>
       <c r="P693" t="s" s="2">
         <v>192</v>
       </c>
@@ -78861,7 +78820,7 @@
         <v>81</v>
       </c>
       <c r="AJ693" t="s" s="2">
-        <v>727</v>
+        <v>73</v>
       </c>
       <c r="AK693" t="s" s="2">
         <v>93</v>
@@ -78872,10 +78831,10 @@
         <v>1383</v>
       </c>
       <c r="B694" t="s" s="2">
-        <v>1457</v>
+        <v>1451</v>
       </c>
       <c r="C694" t="s" s="2">
-        <v>1457</v>
+        <v>1451</v>
       </c>
       <c r="D694" s="2"/>
       <c r="E694" t="s" s="2">
@@ -78906,9 +78865,7 @@
       <c r="N694" t="s" s="2">
         <v>196</v>
       </c>
-      <c r="O694" t="s" s="2">
-        <v>1456</v>
-      </c>
+      <c r="O694" s="2"/>
       <c r="P694" t="s" s="2">
         <v>197</v>
       </c>
@@ -78968,7 +78925,7 @@
         <v>81</v>
       </c>
       <c r="AJ694" t="s" s="2">
-        <v>727</v>
+        <v>73</v>
       </c>
       <c r="AK694" t="s" s="2">
         <v>93</v>
@@ -78979,10 +78936,10 @@
         <v>1383</v>
       </c>
       <c r="B695" t="s" s="2">
-        <v>1458</v>
+        <v>1452</v>
       </c>
       <c r="C695" t="s" s="2">
-        <v>1458</v>
+        <v>1452</v>
       </c>
       <c r="D695" s="2"/>
       <c r="E695" t="s" s="2">
@@ -79075,7 +79032,7 @@
         <v>81</v>
       </c>
       <c r="AJ695" t="s" s="2">
-        <v>727</v>
+        <v>73</v>
       </c>
       <c r="AK695" t="s" s="2">
         <v>93</v>
@@ -79086,10 +79043,10 @@
         <v>1383</v>
       </c>
       <c r="B696" t="s" s="2">
-        <v>1459</v>
+        <v>1453</v>
       </c>
       <c r="C696" t="s" s="2">
-        <v>1459</v>
+        <v>1453</v>
       </c>
       <c r="D696" s="2"/>
       <c r="E696" t="s" s="2">
@@ -79182,7 +79139,7 @@
         <v>81</v>
       </c>
       <c r="AJ696" t="s" s="2">
-        <v>727</v>
+        <v>73</v>
       </c>
       <c r="AK696" t="s" s="2">
         <v>93</v>
@@ -79193,10 +79150,10 @@
         <v>1383</v>
       </c>
       <c r="B697" t="s" s="2">
-        <v>1460</v>
+        <v>1454</v>
       </c>
       <c r="C697" t="s" s="2">
-        <v>1460</v>
+        <v>1454</v>
       </c>
       <c r="D697" s="2"/>
       <c r="E697" t="s" s="2">
@@ -79222,20 +79179,18 @@
         <v>101</v>
       </c>
       <c r="M697" t="s" s="2">
-        <v>1461</v>
+        <v>1455</v>
       </c>
       <c r="N697" t="s" s="2">
-        <v>1462</v>
-      </c>
-      <c r="O697" t="s" s="2">
         <v>1456</v>
       </c>
+      <c r="O697" s="2"/>
       <c r="P697" s="2"/>
       <c r="Q697" t="s" s="2">
         <v>73</v>
       </c>
       <c r="R697" t="s" s="2">
-        <v>1463</v>
+        <v>1457</v>
       </c>
       <c r="S697" t="s" s="2">
         <v>73</v>
@@ -79259,7 +79214,7 @@
         <v>144</v>
       </c>
       <c r="Z697" t="s" s="2">
-        <v>1464</v>
+        <v>1458</v>
       </c>
       <c r="AA697" t="s" s="2">
         <v>249</v>
@@ -79280,7 +79235,7 @@
         <v>73</v>
       </c>
       <c r="AG697" t="s" s="2">
-        <v>1460</v>
+        <v>1454</v>
       </c>
       <c r="AH697" t="s" s="2">
         <v>74</v>
@@ -79289,7 +79244,7 @@
         <v>81</v>
       </c>
       <c r="AJ697" t="s" s="2">
-        <v>727</v>
+        <v>73</v>
       </c>
       <c r="AK697" t="s" s="2">
         <v>93</v>
@@ -79300,10 +79255,10 @@
         <v>1383</v>
       </c>
       <c r="B698" t="s" s="2">
-        <v>1465</v>
+        <v>1459</v>
       </c>
       <c r="C698" t="s" s="2">
-        <v>1465</v>
+        <v>1459</v>
       </c>
       <c r="D698" s="2"/>
       <c r="E698" t="s" s="2">
@@ -79329,22 +79284,22 @@
         <v>200</v>
       </c>
       <c r="M698" t="s" s="2">
-        <v>1466</v>
+        <v>1460</v>
       </c>
       <c r="N698" t="s" s="2">
-        <v>1467</v>
+        <v>1461</v>
       </c>
       <c r="O698" t="s" s="2">
-        <v>1468</v>
+        <v>1462</v>
       </c>
       <c r="P698" t="s" s="2">
-        <v>1469</v>
+        <v>1463</v>
       </c>
       <c r="Q698" t="s" s="2">
         <v>73</v>
       </c>
       <c r="R698" t="s" s="2">
-        <v>1470</v>
+        <v>1464</v>
       </c>
       <c r="S698" t="s" s="2">
         <v>73</v>
@@ -79389,7 +79344,7 @@
         <v>73</v>
       </c>
       <c r="AG698" t="s" s="2">
-        <v>1465</v>
+        <v>1459</v>
       </c>
       <c r="AH698" t="s" s="2">
         <v>74</v>
@@ -79398,7 +79353,7 @@
         <v>81</v>
       </c>
       <c r="AJ698" t="s" s="2">
-        <v>727</v>
+        <v>73</v>
       </c>
       <c r="AK698" t="s" s="2">
         <v>93</v>
@@ -79409,14 +79364,14 @@
         <v>1383</v>
       </c>
       <c r="B699" t="s" s="2">
-        <v>1471</v>
+        <v>1465</v>
       </c>
       <c r="C699" t="s" s="2">
-        <v>1471</v>
+        <v>1465</v>
       </c>
       <c r="D699" s="2"/>
       <c r="E699" t="s" s="2">
-        <v>1472</v>
+        <v>1466</v>
       </c>
       <c r="F699" s="2"/>
       <c r="G699" t="s" s="2">
@@ -79441,10 +79396,10 @@
         <v>213</v>
       </c>
       <c r="N699" t="s" s="2">
-        <v>1473</v>
+        <v>1467</v>
       </c>
       <c r="O699" t="s" s="2">
-        <v>1474</v>
+        <v>1468</v>
       </c>
       <c r="P699" s="2"/>
       <c r="Q699" t="s" s="2">
@@ -79494,7 +79449,7 @@
         <v>73</v>
       </c>
       <c r="AG699" t="s" s="2">
-        <v>1471</v>
+        <v>1465</v>
       </c>
       <c r="AH699" t="s" s="2">
         <v>74</v>
@@ -79503,7 +79458,7 @@
         <v>81</v>
       </c>
       <c r="AJ699" t="s" s="2">
-        <v>727</v>
+        <v>73</v>
       </c>
       <c r="AK699" t="s" s="2">
         <v>93</v>
@@ -79514,10 +79469,10 @@
         <v>1383</v>
       </c>
       <c r="B700" t="s" s="2">
-        <v>1475</v>
+        <v>1469</v>
       </c>
       <c r="C700" t="s" s="2">
-        <v>1475</v>
+        <v>1469</v>
       </c>
       <c r="D700" s="2"/>
       <c r="E700" t="s" s="2">
@@ -79617,10 +79572,10 @@
         <v>1383</v>
       </c>
       <c r="B701" t="s" s="2">
-        <v>1476</v>
+        <v>1470</v>
       </c>
       <c r="C701" t="s" s="2">
-        <v>1476</v>
+        <v>1470</v>
       </c>
       <c r="D701" s="2"/>
       <c r="E701" t="s" s="2">
@@ -79711,7 +79666,7 @@
         <v>75</v>
       </c>
       <c r="AJ701" t="s" s="2">
-        <v>727</v>
+        <v>73</v>
       </c>
       <c r="AK701" t="s" s="2">
         <v>130</v>
@@ -79722,10 +79677,10 @@
         <v>1383</v>
       </c>
       <c r="B702" t="s" s="2">
-        <v>1477</v>
+        <v>1471</v>
       </c>
       <c r="C702" t="s" s="2">
-        <v>1477</v>
+        <v>1471</v>
       </c>
       <c r="D702" s="2"/>
       <c r="E702" t="s" s="2">
@@ -79818,7 +79773,7 @@
         <v>75</v>
       </c>
       <c r="AJ702" t="s" s="2">
-        <v>727</v>
+        <v>73</v>
       </c>
       <c r="AK702" t="s" s="2">
         <v>93</v>
@@ -79829,10 +79784,10 @@
         <v>1383</v>
       </c>
       <c r="B703" t="s" s="2">
-        <v>1478</v>
+        <v>1472</v>
       </c>
       <c r="C703" t="s" s="2">
-        <v>1478</v>
+        <v>1472</v>
       </c>
       <c r="D703" s="2"/>
       <c r="E703" t="s" s="2">
@@ -79932,10 +79887,10 @@
         <v>1383</v>
       </c>
       <c r="B704" t="s" s="2">
-        <v>1479</v>
+        <v>1473</v>
       </c>
       <c r="C704" t="s" s="2">
-        <v>1479</v>
+        <v>1473</v>
       </c>
       <c r="D704" s="2"/>
       <c r="E704" t="s" s="2">
@@ -80026,7 +79981,7 @@
         <v>75</v>
       </c>
       <c r="AJ704" t="s" s="2">
-        <v>727</v>
+        <v>73</v>
       </c>
       <c r="AK704" t="s" s="2">
         <v>130</v>
@@ -80037,10 +79992,10 @@
         <v>1383</v>
       </c>
       <c r="B705" t="s" s="2">
-        <v>1480</v>
+        <v>1474</v>
       </c>
       <c r="C705" t="s" s="2">
-        <v>1480</v>
+        <v>1474</v>
       </c>
       <c r="D705" s="2"/>
       <c r="E705" t="s" s="2">
@@ -80133,7 +80088,7 @@
         <v>81</v>
       </c>
       <c r="AJ705" t="s" s="2">
-        <v>727</v>
+        <v>73</v>
       </c>
       <c r="AK705" t="s" s="2">
         <v>93</v>
@@ -80144,10 +80099,10 @@
         <v>1383</v>
       </c>
       <c r="B706" t="s" s="2">
-        <v>1481</v>
+        <v>1475</v>
       </c>
       <c r="C706" t="s" s="2">
-        <v>1481</v>
+        <v>1475</v>
       </c>
       <c r="D706" s="2"/>
       <c r="E706" t="s" s="2">
@@ -80238,7 +80193,7 @@
         <v>81</v>
       </c>
       <c r="AJ706" t="s" s="2">
-        <v>727</v>
+        <v>73</v>
       </c>
       <c r="AK706" t="s" s="2">
         <v>93</v>
@@ -80249,10 +80204,10 @@
         <v>1383</v>
       </c>
       <c r="B707" t="s" s="2">
-        <v>1482</v>
+        <v>1476</v>
       </c>
       <c r="C707" t="s" s="2">
-        <v>1482</v>
+        <v>1476</v>
       </c>
       <c r="D707" s="2"/>
       <c r="E707" t="s" s="2">
@@ -80283,9 +80238,7 @@
       <c r="N707" t="s" s="2">
         <v>191</v>
       </c>
-      <c r="O707" t="s" s="2">
-        <v>1456</v>
-      </c>
+      <c r="O707" s="2"/>
       <c r="P707" t="s" s="2">
         <v>192</v>
       </c>
@@ -80345,7 +80298,7 @@
         <v>81</v>
       </c>
       <c r="AJ707" t="s" s="2">
-        <v>727</v>
+        <v>73</v>
       </c>
       <c r="AK707" t="s" s="2">
         <v>93</v>
@@ -80356,10 +80309,10 @@
         <v>1383</v>
       </c>
       <c r="B708" t="s" s="2">
-        <v>1483</v>
+        <v>1477</v>
       </c>
       <c r="C708" t="s" s="2">
-        <v>1483</v>
+        <v>1477</v>
       </c>
       <c r="D708" s="2"/>
       <c r="E708" t="s" s="2">
@@ -80390,9 +80343,7 @@
       <c r="N708" t="s" s="2">
         <v>196</v>
       </c>
-      <c r="O708" t="s" s="2">
-        <v>1456</v>
-      </c>
+      <c r="O708" s="2"/>
       <c r="P708" t="s" s="2">
         <v>197</v>
       </c>
@@ -80452,7 +80403,7 @@
         <v>81</v>
       </c>
       <c r="AJ708" t="s" s="2">
-        <v>727</v>
+        <v>73</v>
       </c>
       <c r="AK708" t="s" s="2">
         <v>93</v>
@@ -80463,10 +80414,10 @@
         <v>1383</v>
       </c>
       <c r="B709" t="s" s="2">
-        <v>1484</v>
+        <v>1478</v>
       </c>
       <c r="C709" t="s" s="2">
-        <v>1484</v>
+        <v>1478</v>
       </c>
       <c r="D709" s="2"/>
       <c r="E709" t="s" s="2">
@@ -80559,7 +80510,7 @@
         <v>81</v>
       </c>
       <c r="AJ709" t="s" s="2">
-        <v>727</v>
+        <v>73</v>
       </c>
       <c r="AK709" t="s" s="2">
         <v>93</v>
@@ -80570,10 +80521,10 @@
         <v>1383</v>
       </c>
       <c r="B710" t="s" s="2">
-        <v>1485</v>
+        <v>1479</v>
       </c>
       <c r="C710" t="s" s="2">
-        <v>1485</v>
+        <v>1479</v>
       </c>
       <c r="D710" s="2"/>
       <c r="E710" t="s" s="2">
@@ -80666,7 +80617,7 @@
         <v>81</v>
       </c>
       <c r="AJ710" t="s" s="2">
-        <v>727</v>
+        <v>73</v>
       </c>
       <c r="AK710" t="s" s="2">
         <v>93</v>
@@ -80677,14 +80628,14 @@
         <v>1383</v>
       </c>
       <c r="B711" t="s" s="2">
-        <v>1486</v>
+        <v>1480</v>
       </c>
       <c r="C711" t="s" s="2">
-        <v>1486</v>
+        <v>1480</v>
       </c>
       <c r="D711" s="2"/>
       <c r="E711" t="s" s="2">
-        <v>1487</v>
+        <v>1481</v>
       </c>
       <c r="F711" s="2"/>
       <c r="G711" t="s" s="2">
@@ -80706,13 +80657,13 @@
         <v>148</v>
       </c>
       <c r="M711" t="s" s="2">
-        <v>1488</v>
+        <v>1482</v>
       </c>
       <c r="N711" t="s" s="2">
-        <v>1489</v>
+        <v>1483</v>
       </c>
       <c r="O711" t="s" s="2">
-        <v>1490</v>
+        <v>1484</v>
       </c>
       <c r="P711" s="2"/>
       <c r="Q711" t="s" s="2">
@@ -80741,10 +80692,10 @@
         <v>151</v>
       </c>
       <c r="Z711" t="s" s="2">
-        <v>1491</v>
+        <v>1485</v>
       </c>
       <c r="AA711" t="s" s="2">
-        <v>1492</v>
+        <v>1486</v>
       </c>
       <c r="AB711" t="s" s="2">
         <v>73</v>
@@ -80762,7 +80713,7 @@
         <v>73</v>
       </c>
       <c r="AG711" t="s" s="2">
-        <v>1486</v>
+        <v>1480</v>
       </c>
       <c r="AH711" t="s" s="2">
         <v>74</v>
@@ -80771,7 +80722,7 @@
         <v>75</v>
       </c>
       <c r="AJ711" t="s" s="2">
-        <v>1493</v>
+        <v>1487</v>
       </c>
       <c r="AK711" t="s" s="2">
         <v>93</v>
@@ -80782,10 +80733,10 @@
         <v>1383</v>
       </c>
       <c r="B712" t="s" s="2">
-        <v>1494</v>
+        <v>1488</v>
       </c>
       <c r="C712" t="s" s="2">
-        <v>1494</v>
+        <v>1488</v>
       </c>
       <c r="D712" s="2"/>
       <c r="E712" t="s" s="2">
@@ -80808,17 +80759,17 @@
         <v>82</v>
       </c>
       <c r="L712" t="s" s="2">
-        <v>1495</v>
+        <v>1489</v>
       </c>
       <c r="M712" t="s" s="2">
-        <v>1496</v>
+        <v>1490</v>
       </c>
       <c r="N712" t="s" s="2">
-        <v>1497</v>
+        <v>1491</v>
       </c>
       <c r="O712" s="2"/>
       <c r="P712" t="s" s="2">
-        <v>1498</v>
+        <v>1492</v>
       </c>
       <c r="Q712" t="s" s="2">
         <v>73</v>
@@ -80867,7 +80818,7 @@
         <v>73</v>
       </c>
       <c r="AG712" t="s" s="2">
-        <v>1494</v>
+        <v>1488</v>
       </c>
       <c r="AH712" t="s" s="2">
         <v>74</v>
@@ -80876,7 +80827,7 @@
         <v>81</v>
       </c>
       <c r="AJ712" t="s" s="2">
-        <v>727</v>
+        <v>73</v>
       </c>
       <c r="AK712" t="s" s="2">
         <v>93</v>
@@ -80887,10 +80838,10 @@
         <v>1383</v>
       </c>
       <c r="B713" t="s" s="2">
-        <v>1499</v>
+        <v>1493</v>
       </c>
       <c r="C713" t="s" s="2">
-        <v>1499</v>
+        <v>1493</v>
       </c>
       <c r="D713" s="2"/>
       <c r="E713" t="s" s="2">
@@ -80919,11 +80870,9 @@
         <v>415</v>
       </c>
       <c r="N713" t="s" s="2">
-        <v>1500</v>
-      </c>
-      <c r="O713" t="s" s="2">
-        <v>1419</v>
-      </c>
+        <v>1494</v>
+      </c>
+      <c r="O713" s="2"/>
       <c r="P713" s="2"/>
       <c r="Q713" t="s" s="2">
         <v>73</v>
@@ -80972,7 +80921,7 @@
         <v>73</v>
       </c>
       <c r="AG713" t="s" s="2">
-        <v>1499</v>
+        <v>1493</v>
       </c>
       <c r="AH713" t="s" s="2">
         <v>81</v>
@@ -80981,10 +80930,10 @@
         <v>81</v>
       </c>
       <c r="AJ713" t="s" s="2">
-        <v>727</v>
+        <v>73</v>
       </c>
       <c r="AK713" t="s" s="2">
-        <v>1420</v>
+        <v>93</v>
       </c>
     </row>
     <row r="714">
@@ -80992,10 +80941,10 @@
         <v>1383</v>
       </c>
       <c r="B714" t="s" s="2">
-        <v>1501</v>
+        <v>1495</v>
       </c>
       <c r="C714" t="s" s="2">
-        <v>1501</v>
+        <v>1495</v>
       </c>
       <c r="D714" s="2"/>
       <c r="E714" t="s" s="2">
@@ -81095,10 +81044,10 @@
         <v>1383</v>
       </c>
       <c r="B715" t="s" s="2">
-        <v>1502</v>
+        <v>1496</v>
       </c>
       <c r="C715" t="s" s="2">
-        <v>1502</v>
+        <v>1496</v>
       </c>
       <c r="D715" s="2"/>
       <c r="E715" t="s" s="2">
@@ -81189,7 +81138,7 @@
         <v>75</v>
       </c>
       <c r="AJ715" t="s" s="2">
-        <v>727</v>
+        <v>73</v>
       </c>
       <c r="AK715" t="s" s="2">
         <v>130</v>
@@ -81200,10 +81149,10 @@
         <v>1383</v>
       </c>
       <c r="B716" t="s" s="2">
-        <v>1503</v>
+        <v>1497</v>
       </c>
       <c r="C716" t="s" s="2">
-        <v>1503</v>
+        <v>1497</v>
       </c>
       <c r="D716" s="2"/>
       <c r="E716" t="s" s="2">
@@ -81294,7 +81243,7 @@
         <v>81</v>
       </c>
       <c r="AJ716" t="s" s="2">
-        <v>1504</v>
+        <v>277</v>
       </c>
       <c r="AK716" t="s" s="2">
         <v>93</v>
@@ -81305,10 +81254,10 @@
         <v>1383</v>
       </c>
       <c r="B717" t="s" s="2">
-        <v>1505</v>
+        <v>1498</v>
       </c>
       <c r="C717" t="s" s="2">
-        <v>1505</v>
+        <v>1498</v>
       </c>
       <c r="D717" s="2"/>
       <c r="E717" t="s" s="2">
@@ -81399,7 +81348,7 @@
         <v>81</v>
       </c>
       <c r="AJ717" t="s" s="2">
-        <v>727</v>
+        <v>73</v>
       </c>
       <c r="AK717" t="s" s="2">
         <v>93</v>
@@ -81410,10 +81359,10 @@
         <v>1383</v>
       </c>
       <c r="B718" t="s" s="2">
-        <v>1506</v>
+        <v>1499</v>
       </c>
       <c r="C718" t="s" s="2">
-        <v>1506</v>
+        <v>1499</v>
       </c>
       <c r="D718" s="2"/>
       <c r="E718" t="s" s="2">
@@ -81504,7 +81453,7 @@
         <v>81</v>
       </c>
       <c r="AJ718" t="s" s="2">
-        <v>727</v>
+        <v>73</v>
       </c>
       <c r="AK718" t="s" s="2">
         <v>93</v>
@@ -81515,10 +81464,10 @@
         <v>1383</v>
       </c>
       <c r="B719" t="s" s="2">
-        <v>1507</v>
+        <v>1500</v>
       </c>
       <c r="C719" t="s" s="2">
-        <v>1507</v>
+        <v>1500</v>
       </c>
       <c r="D719" s="2"/>
       <c r="E719" t="s" s="2">
@@ -81618,10 +81567,10 @@
         <v>1383</v>
       </c>
       <c r="B720" t="s" s="2">
-        <v>1508</v>
+        <v>1501</v>
       </c>
       <c r="C720" t="s" s="2">
-        <v>1508</v>
+        <v>1501</v>
       </c>
       <c r="D720" s="2"/>
       <c r="E720" t="s" s="2">
@@ -81712,7 +81661,7 @@
         <v>75</v>
       </c>
       <c r="AJ720" t="s" s="2">
-        <v>727</v>
+        <v>73</v>
       </c>
       <c r="AK720" t="s" s="2">
         <v>130</v>
@@ -81723,10 +81672,10 @@
         <v>1383</v>
       </c>
       <c r="B721" t="s" s="2">
-        <v>1509</v>
+        <v>1502</v>
       </c>
       <c r="C721" t="s" s="2">
-        <v>1509</v>
+        <v>1502</v>
       </c>
       <c r="D721" s="2"/>
       <c r="E721" t="s" s="2">
@@ -81819,7 +81768,7 @@
         <v>81</v>
       </c>
       <c r="AJ721" t="s" s="2">
-        <v>727</v>
+        <v>73</v>
       </c>
       <c r="AK721" t="s" s="2">
         <v>93</v>
@@ -81830,10 +81779,10 @@
         <v>1383</v>
       </c>
       <c r="B722" t="s" s="2">
-        <v>1510</v>
+        <v>1503</v>
       </c>
       <c r="C722" t="s" s="2">
-        <v>1510</v>
+        <v>1503</v>
       </c>
       <c r="D722" s="2"/>
       <c r="E722" t="s" s="2">
@@ -81926,7 +81875,7 @@
         <v>81</v>
       </c>
       <c r="AJ722" t="s" s="2">
-        <v>727</v>
+        <v>73</v>
       </c>
       <c r="AK722" t="s" s="2">
         <v>93</v>
@@ -81937,10 +81886,10 @@
         <v>1383</v>
       </c>
       <c r="B723" t="s" s="2">
-        <v>1511</v>
+        <v>1504</v>
       </c>
       <c r="C723" t="s" s="2">
-        <v>1511</v>
+        <v>1504</v>
       </c>
       <c r="D723" s="2"/>
       <c r="E723" t="s" s="2">
@@ -82033,7 +81982,7 @@
         <v>81</v>
       </c>
       <c r="AJ723" t="s" s="2">
-        <v>727</v>
+        <v>73</v>
       </c>
       <c r="AK723" t="s" s="2">
         <v>93</v>
@@ -82044,10 +81993,10 @@
         <v>1383</v>
       </c>
       <c r="B724" t="s" s="2">
-        <v>1512</v>
+        <v>1505</v>
       </c>
       <c r="C724" t="s" s="2">
-        <v>1512</v>
+        <v>1505</v>
       </c>
       <c r="D724" s="2"/>
       <c r="E724" t="s" s="2">
@@ -82079,7 +82028,7 @@
         <v>341</v>
       </c>
       <c r="O724" t="s" s="2">
-        <v>1513</v>
+        <v>342</v>
       </c>
       <c r="P724" s="2"/>
       <c r="Q724" t="s" s="2">
@@ -82138,7 +82087,7 @@
         <v>81</v>
       </c>
       <c r="AJ724" t="s" s="2">
-        <v>727</v>
+        <v>73</v>
       </c>
       <c r="AK724" t="s" s="2">
         <v>93</v>
@@ -82149,10 +82098,10 @@
         <v>1383</v>
       </c>
       <c r="B725" t="s" s="2">
-        <v>1514</v>
+        <v>1506</v>
       </c>
       <c r="C725" t="s" s="2">
-        <v>1514</v>
+        <v>1506</v>
       </c>
       <c r="D725" s="2"/>
       <c r="E725" t="s" s="2">
@@ -82183,9 +82132,7 @@
       <c r="N725" t="s" s="2">
         <v>348</v>
       </c>
-      <c r="O725" t="s" s="2">
-        <v>1515</v>
-      </c>
+      <c r="O725" s="2"/>
       <c r="P725" s="2"/>
       <c r="Q725" t="s" s="2">
         <v>73</v>
@@ -82243,10 +82190,10 @@
         <v>81</v>
       </c>
       <c r="AJ725" t="s" s="2">
-        <v>727</v>
+        <v>73</v>
       </c>
       <c r="AK725" t="s" s="2">
-        <v>1516</v>
+        <v>93</v>
       </c>
     </row>
     <row r="726">
@@ -82254,10 +82201,10 @@
         <v>1383</v>
       </c>
       <c r="B726" t="s" s="2">
-        <v>1517</v>
+        <v>1507</v>
       </c>
       <c r="C726" t="s" s="2">
-        <v>1517</v>
+        <v>1507</v>
       </c>
       <c r="D726" s="2"/>
       <c r="E726" t="s" s="2">
@@ -82348,10 +82295,10 @@
         <v>81</v>
       </c>
       <c r="AJ726" t="s" s="2">
-        <v>727</v>
+        <v>73</v>
       </c>
       <c r="AK726" t="s" s="2">
-        <v>1420</v>
+        <v>93</v>
       </c>
     </row>
     <row r="727">
@@ -82359,10 +82306,10 @@
         <v>1383</v>
       </c>
       <c r="B727" t="s" s="2">
-        <v>1518</v>
+        <v>1508</v>
       </c>
       <c r="C727" t="s" s="2">
-        <v>1518</v>
+        <v>1508</v>
       </c>
       <c r="D727" s="2"/>
       <c r="E727" t="s" s="2">
@@ -82453,7 +82400,7 @@
         <v>81</v>
       </c>
       <c r="AJ727" t="s" s="2">
-        <v>727</v>
+        <v>73</v>
       </c>
       <c r="AK727" t="s" s="2">
         <v>93</v>
@@ -82464,14 +82411,14 @@
         <v>1383</v>
       </c>
       <c r="B728" t="s" s="2">
-        <v>1519</v>
+        <v>1509</v>
       </c>
       <c r="C728" t="s" s="2">
-        <v>1519</v>
+        <v>1509</v>
       </c>
       <c r="D728" s="2"/>
       <c r="E728" t="s" s="2">
-        <v>1520</v>
+        <v>1510</v>
       </c>
       <c r="F728" s="2"/>
       <c r="G728" t="s" s="2">
@@ -82493,14 +82440,12 @@
         <v>627</v>
       </c>
       <c r="M728" t="s" s="2">
-        <v>1521</v>
+        <v>1511</v>
       </c>
       <c r="N728" t="s" s="2">
-        <v>1522</v>
-      </c>
-      <c r="O728" t="s" s="2">
-        <v>1419</v>
-      </c>
+        <v>1512</v>
+      </c>
+      <c r="O728" s="2"/>
       <c r="P728" s="2"/>
       <c r="Q728" t="s" s="2">
         <v>73</v>
@@ -82549,7 +82494,7 @@
         <v>73</v>
       </c>
       <c r="AG728" t="s" s="2">
-        <v>1519</v>
+        <v>1509</v>
       </c>
       <c r="AH728" t="s" s="2">
         <v>74</v>
@@ -82558,10 +82503,10 @@
         <v>81</v>
       </c>
       <c r="AJ728" t="s" s="2">
-        <v>727</v>
+        <v>73</v>
       </c>
       <c r="AK728" t="s" s="2">
-        <v>1420</v>
+        <v>93</v>
       </c>
     </row>
     <row r="729">
@@ -82569,14 +82514,14 @@
         <v>1383</v>
       </c>
       <c r="B729" t="s" s="2">
-        <v>1523</v>
+        <v>1513</v>
       </c>
       <c r="C729" t="s" s="2">
-        <v>1523</v>
+        <v>1513</v>
       </c>
       <c r="D729" s="2"/>
       <c r="E729" t="s" s="2">
-        <v>1524</v>
+        <v>1514</v>
       </c>
       <c r="F729" s="2"/>
       <c r="G729" t="s" s="2">
@@ -82598,10 +82543,10 @@
         <v>391</v>
       </c>
       <c r="M729" t="s" s="2">
-        <v>1525</v>
+        <v>1515</v>
       </c>
       <c r="N729" t="s" s="2">
-        <v>1526</v>
+        <v>1516</v>
       </c>
       <c r="O729" s="2"/>
       <c r="P729" s="2"/>
@@ -82652,7 +82597,7 @@
         <v>73</v>
       </c>
       <c r="AG729" t="s" s="2">
-        <v>1523</v>
+        <v>1513</v>
       </c>
       <c r="AH729" t="s" s="2">
         <v>74</v>
@@ -82661,7 +82606,7 @@
         <v>81</v>
       </c>
       <c r="AJ729" t="s" s="2">
-        <v>727</v>
+        <v>73</v>
       </c>
       <c r="AK729" t="s" s="2">
         <v>93</v>
@@ -82672,10 +82617,10 @@
         <v>1383</v>
       </c>
       <c r="B730" t="s" s="2">
-        <v>1527</v>
+        <v>1517</v>
       </c>
       <c r="C730" t="s" s="2">
-        <v>1527</v>
+        <v>1517</v>
       </c>
       <c r="D730" s="2"/>
       <c r="E730" t="s" s="2">
@@ -82701,10 +82646,10 @@
         <v>159</v>
       </c>
       <c r="M730" t="s" s="2">
-        <v>160</v>
+        <v>1518</v>
       </c>
       <c r="N730" t="s" s="2">
-        <v>161</v>
+        <v>1519</v>
       </c>
       <c r="O730" s="2"/>
       <c r="P730" s="2"/>
@@ -82775,10 +82720,10 @@
         <v>1383</v>
       </c>
       <c r="B731" t="s" s="2">
-        <v>1528</v>
+        <v>1520</v>
       </c>
       <c r="C731" t="s" s="2">
-        <v>1528</v>
+        <v>1520</v>
       </c>
       <c r="D731" s="2"/>
       <c r="E731" t="s" s="2">
@@ -82807,7 +82752,7 @@
         <v>126</v>
       </c>
       <c r="N731" t="s" s="2">
-        <v>164</v>
+        <v>127</v>
       </c>
       <c r="O731" t="s" s="2">
         <v>128</v>
@@ -82848,16 +82793,16 @@
         <v>73</v>
       </c>
       <c r="AC731" t="s" s="2">
-        <v>165</v>
+        <v>73</v>
       </c>
       <c r="AD731" t="s" s="2">
-        <v>166</v>
+        <v>73</v>
       </c>
       <c r="AE731" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AF731" t="s" s="2">
-        <v>167</v>
+        <v>73</v>
       </c>
       <c r="AG731" t="s" s="2">
         <v>168</v>
@@ -82869,7 +82814,7 @@
         <v>75</v>
       </c>
       <c r="AJ731" t="s" s="2">
-        <v>727</v>
+        <v>73</v>
       </c>
       <c r="AK731" t="s" s="2">
         <v>130</v>
@@ -82880,10 +82825,10 @@
         <v>1383</v>
       </c>
       <c r="B732" t="s" s="2">
-        <v>1529</v>
+        <v>1521</v>
       </c>
       <c r="C732" t="s" s="2">
-        <v>1529</v>
+        <v>1521</v>
       </c>
       <c r="D732" s="2"/>
       <c r="E732" t="s" s="2">
@@ -82909,10 +82854,10 @@
         <v>391</v>
       </c>
       <c r="M732" t="s" s="2">
-        <v>1530</v>
+        <v>1522</v>
       </c>
       <c r="N732" t="s" s="2">
-        <v>1530</v>
+        <v>1523</v>
       </c>
       <c r="O732" s="2"/>
       <c r="P732" s="2"/>
@@ -82963,7 +82908,7 @@
         <v>73</v>
       </c>
       <c r="AG732" t="s" s="2">
-        <v>1531</v>
+        <v>1524</v>
       </c>
       <c r="AH732" t="s" s="2">
         <v>74</v>
@@ -82983,10 +82928,10 @@
         <v>1383</v>
       </c>
       <c r="B733" t="s" s="2">
-        <v>1532</v>
+        <v>1525</v>
       </c>
       <c r="C733" t="s" s="2">
-        <v>1532</v>
+        <v>1525</v>
       </c>
       <c r="D733" s="2"/>
       <c r="E733" t="s" s="2">
@@ -83009,13 +82954,13 @@
         <v>82</v>
       </c>
       <c r="L733" t="s" s="2">
-        <v>1533</v>
+        <v>1526</v>
       </c>
       <c r="M733" t="s" s="2">
-        <v>1534</v>
+        <v>1527</v>
       </c>
       <c r="N733" t="s" s="2">
-        <v>1535</v>
+        <v>1528</v>
       </c>
       <c r="O733" s="2"/>
       <c r="P733" s="2"/>
@@ -83045,10 +82990,10 @@
         <v>151</v>
       </c>
       <c r="Z733" t="s" s="2">
-        <v>1536</v>
+        <v>1529</v>
       </c>
       <c r="AA733" t="s" s="2">
-        <v>1537</v>
+        <v>1530</v>
       </c>
       <c r="AB733" t="s" s="2">
         <v>73</v>
@@ -83066,7 +83011,7 @@
         <v>73</v>
       </c>
       <c r="AG733" t="s" s="2">
-        <v>1532</v>
+        <v>1525</v>
       </c>
       <c r="AH733" t="s" s="2">
         <v>74</v>
@@ -83075,7 +83020,7 @@
         <v>81</v>
       </c>
       <c r="AJ733" t="s" s="2">
-        <v>727</v>
+        <v>73</v>
       </c>
       <c r="AK733" t="s" s="2">
         <v>93</v>
@@ -83086,14 +83031,14 @@
         <v>1383</v>
       </c>
       <c r="B734" t="s" s="2">
-        <v>1538</v>
+        <v>1531</v>
       </c>
       <c r="C734" t="s" s="2">
-        <v>1538</v>
+        <v>1531</v>
       </c>
       <c r="D734" s="2"/>
       <c r="E734" t="s" s="2">
-        <v>1539</v>
+        <v>1532</v>
       </c>
       <c r="F734" s="2"/>
       <c r="G734" t="s" s="2">
@@ -83115,10 +83060,10 @@
         <v>391</v>
       </c>
       <c r="M734" t="s" s="2">
-        <v>1540</v>
+        <v>1533</v>
       </c>
       <c r="N734" t="s" s="2">
-        <v>1541</v>
+        <v>1534</v>
       </c>
       <c r="O734" s="2"/>
       <c r="P734" s="2"/>
@@ -83169,7 +83114,7 @@
         <v>73</v>
       </c>
       <c r="AG734" t="s" s="2">
-        <v>1538</v>
+        <v>1531</v>
       </c>
       <c r="AH734" t="s" s="2">
         <v>74</v>
@@ -83178,7 +83123,7 @@
         <v>81</v>
       </c>
       <c r="AJ734" t="s" s="2">
-        <v>727</v>
+        <v>73</v>
       </c>
       <c r="AK734" t="s" s="2">
         <v>93</v>
@@ -83189,14 +83134,14 @@
         <v>1383</v>
       </c>
       <c r="B735" t="s" s="2">
-        <v>1542</v>
+        <v>1535</v>
       </c>
       <c r="C735" t="s" s="2">
-        <v>1542</v>
+        <v>1535</v>
       </c>
       <c r="D735" s="2"/>
       <c r="E735" t="s" s="2">
-        <v>1543</v>
+        <v>1536</v>
       </c>
       <c r="F735" s="2"/>
       <c r="G735" t="s" s="2">
@@ -83218,13 +83163,13 @@
         <v>305</v>
       </c>
       <c r="M735" t="s" s="2">
-        <v>1544</v>
+        <v>1537</v>
       </c>
       <c r="N735" t="s" s="2">
-        <v>1545</v>
+        <v>1538</v>
       </c>
       <c r="O735" t="s" s="2">
-        <v>1546</v>
+        <v>1539</v>
       </c>
       <c r="P735" s="2"/>
       <c r="Q735" t="s" s="2">
@@ -83274,7 +83219,7 @@
         <v>73</v>
       </c>
       <c r="AG735" t="s" s="2">
-        <v>1542</v>
+        <v>1535</v>
       </c>
       <c r="AH735" t="s" s="2">
         <v>74</v>
@@ -83283,10 +83228,10 @@
         <v>81</v>
       </c>
       <c r="AJ735" t="s" s="2">
-        <v>727</v>
+        <v>73</v>
       </c>
       <c r="AK735" t="s" s="2">
-        <v>1420</v>
+        <v>93</v>
       </c>
     </row>
     <row r="736">
@@ -83294,10 +83239,10 @@
         <v>1383</v>
       </c>
       <c r="B736" t="s" s="2">
-        <v>1547</v>
+        <v>1540</v>
       </c>
       <c r="C736" t="s" s="2">
-        <v>1547</v>
+        <v>1540</v>
       </c>
       <c r="D736" s="2"/>
       <c r="E736" t="s" s="2">
@@ -83397,10 +83342,10 @@
         <v>1383</v>
       </c>
       <c r="B737" t="s" s="2">
-        <v>1548</v>
+        <v>1541</v>
       </c>
       <c r="C737" t="s" s="2">
-        <v>1548</v>
+        <v>1541</v>
       </c>
       <c r="D737" s="2"/>
       <c r="E737" t="s" s="2">
@@ -83491,7 +83436,7 @@
         <v>75</v>
       </c>
       <c r="AJ737" t="s" s="2">
-        <v>727</v>
+        <v>73</v>
       </c>
       <c r="AK737" t="s" s="2">
         <v>130</v>
@@ -83502,10 +83447,10 @@
         <v>1383</v>
       </c>
       <c r="B738" t="s" s="2">
-        <v>1549</v>
+        <v>1542</v>
       </c>
       <c r="C738" t="s" s="2">
-        <v>1549</v>
+        <v>1542</v>
       </c>
       <c r="D738" s="2"/>
       <c r="E738" t="s" s="2">
@@ -83596,7 +83541,7 @@
         <v>81</v>
       </c>
       <c r="AJ738" t="s" s="2">
-        <v>1504</v>
+        <v>277</v>
       </c>
       <c r="AK738" t="s" s="2">
         <v>93</v>
@@ -83607,10 +83552,10 @@
         <v>1383</v>
       </c>
       <c r="B739" t="s" s="2">
-        <v>1550</v>
+        <v>1543</v>
       </c>
       <c r="C739" t="s" s="2">
-        <v>1550</v>
+        <v>1543</v>
       </c>
       <c r="D739" s="2"/>
       <c r="E739" t="s" s="2">
@@ -83701,7 +83646,7 @@
         <v>81</v>
       </c>
       <c r="AJ739" t="s" s="2">
-        <v>727</v>
+        <v>73</v>
       </c>
       <c r="AK739" t="s" s="2">
         <v>93</v>
@@ -83712,10 +83657,10 @@
         <v>1383</v>
       </c>
       <c r="B740" t="s" s="2">
-        <v>1551</v>
+        <v>1544</v>
       </c>
       <c r="C740" t="s" s="2">
-        <v>1551</v>
+        <v>1544</v>
       </c>
       <c r="D740" s="2"/>
       <c r="E740" t="s" s="2">
@@ -83806,7 +83751,7 @@
         <v>81</v>
       </c>
       <c r="AJ740" t="s" s="2">
-        <v>727</v>
+        <v>73</v>
       </c>
       <c r="AK740" t="s" s="2">
         <v>93</v>
@@ -83817,10 +83762,10 @@
         <v>1383</v>
       </c>
       <c r="B741" t="s" s="2">
-        <v>1552</v>
+        <v>1545</v>
       </c>
       <c r="C741" t="s" s="2">
-        <v>1552</v>
+        <v>1545</v>
       </c>
       <c r="D741" s="2"/>
       <c r="E741" t="s" s="2">
@@ -83920,10 +83865,10 @@
         <v>1383</v>
       </c>
       <c r="B742" t="s" s="2">
-        <v>1553</v>
+        <v>1546</v>
       </c>
       <c r="C742" t="s" s="2">
-        <v>1553</v>
+        <v>1546</v>
       </c>
       <c r="D742" s="2"/>
       <c r="E742" t="s" s="2">
@@ -84014,7 +83959,7 @@
         <v>75</v>
       </c>
       <c r="AJ742" t="s" s="2">
-        <v>727</v>
+        <v>73</v>
       </c>
       <c r="AK742" t="s" s="2">
         <v>130</v>
@@ -84025,10 +83970,10 @@
         <v>1383</v>
       </c>
       <c r="B743" t="s" s="2">
-        <v>1554</v>
+        <v>1547</v>
       </c>
       <c r="C743" t="s" s="2">
-        <v>1554</v>
+        <v>1547</v>
       </c>
       <c r="D743" s="2"/>
       <c r="E743" t="s" s="2">
@@ -84121,7 +84066,7 @@
         <v>81</v>
       </c>
       <c r="AJ743" t="s" s="2">
-        <v>727</v>
+        <v>73</v>
       </c>
       <c r="AK743" t="s" s="2">
         <v>93</v>
@@ -84132,10 +84077,10 @@
         <v>1383</v>
       </c>
       <c r="B744" t="s" s="2">
-        <v>1555</v>
+        <v>1548</v>
       </c>
       <c r="C744" t="s" s="2">
-        <v>1555</v>
+        <v>1548</v>
       </c>
       <c r="D744" s="2"/>
       <c r="E744" t="s" s="2">
@@ -84228,7 +84173,7 @@
         <v>81</v>
       </c>
       <c r="AJ744" t="s" s="2">
-        <v>727</v>
+        <v>73</v>
       </c>
       <c r="AK744" t="s" s="2">
         <v>93</v>
@@ -84239,10 +84184,10 @@
         <v>1383</v>
       </c>
       <c r="B745" t="s" s="2">
-        <v>1556</v>
+        <v>1549</v>
       </c>
       <c r="C745" t="s" s="2">
-        <v>1556</v>
+        <v>1549</v>
       </c>
       <c r="D745" s="2"/>
       <c r="E745" t="s" s="2">
@@ -84335,7 +84280,7 @@
         <v>81</v>
       </c>
       <c r="AJ745" t="s" s="2">
-        <v>727</v>
+        <v>73</v>
       </c>
       <c r="AK745" t="s" s="2">
         <v>93</v>
@@ -84346,10 +84291,10 @@
         <v>1383</v>
       </c>
       <c r="B746" t="s" s="2">
-        <v>1557</v>
+        <v>1550</v>
       </c>
       <c r="C746" t="s" s="2">
-        <v>1557</v>
+        <v>1550</v>
       </c>
       <c r="D746" s="2"/>
       <c r="E746" t="s" s="2">
@@ -84381,7 +84326,7 @@
         <v>341</v>
       </c>
       <c r="O746" t="s" s="2">
-        <v>1513</v>
+        <v>342</v>
       </c>
       <c r="P746" s="2"/>
       <c r="Q746" t="s" s="2">
@@ -84440,7 +84385,7 @@
         <v>81</v>
       </c>
       <c r="AJ746" t="s" s="2">
-        <v>727</v>
+        <v>73</v>
       </c>
       <c r="AK746" t="s" s="2">
         <v>93</v>
@@ -84451,10 +84396,10 @@
         <v>1383</v>
       </c>
       <c r="B747" t="s" s="2">
-        <v>1558</v>
+        <v>1551</v>
       </c>
       <c r="C747" t="s" s="2">
-        <v>1558</v>
+        <v>1551</v>
       </c>
       <c r="D747" s="2"/>
       <c r="E747" t="s" s="2">
@@ -84485,9 +84430,7 @@
       <c r="N747" t="s" s="2">
         <v>348</v>
       </c>
-      <c r="O747" t="s" s="2">
-        <v>1515</v>
-      </c>
+      <c r="O747" s="2"/>
       <c r="P747" s="2"/>
       <c r="Q747" t="s" s="2">
         <v>73</v>
@@ -84545,10 +84488,10 @@
         <v>81</v>
       </c>
       <c r="AJ747" t="s" s="2">
-        <v>727</v>
+        <v>73</v>
       </c>
       <c r="AK747" t="s" s="2">
-        <v>1516</v>
+        <v>93</v>
       </c>
     </row>
     <row r="748">
@@ -84556,10 +84499,10 @@
         <v>1383</v>
       </c>
       <c r="B748" t="s" s="2">
-        <v>1559</v>
+        <v>1552</v>
       </c>
       <c r="C748" t="s" s="2">
-        <v>1559</v>
+        <v>1552</v>
       </c>
       <c r="D748" s="2"/>
       <c r="E748" t="s" s="2">
@@ -84650,10 +84593,10 @@
         <v>81</v>
       </c>
       <c r="AJ748" t="s" s="2">
-        <v>727</v>
+        <v>73</v>
       </c>
       <c r="AK748" t="s" s="2">
-        <v>1420</v>
+        <v>93</v>
       </c>
     </row>
     <row r="749">
@@ -84661,10 +84604,10 @@
         <v>1383</v>
       </c>
       <c r="B749" t="s" s="2">
-        <v>1560</v>
+        <v>1553</v>
       </c>
       <c r="C749" t="s" s="2">
-        <v>1560</v>
+        <v>1553</v>
       </c>
       <c r="D749" s="2"/>
       <c r="E749" t="s" s="2">
@@ -84755,7 +84698,7 @@
         <v>81</v>
       </c>
       <c r="AJ749" t="s" s="2">
-        <v>727</v>
+        <v>73</v>
       </c>
       <c r="AK749" t="s" s="2">
         <v>93</v>
@@ -84766,14 +84709,14 @@
         <v>1383</v>
       </c>
       <c r="B750" t="s" s="2">
-        <v>1561</v>
+        <v>1554</v>
       </c>
       <c r="C750" t="s" s="2">
-        <v>1561</v>
+        <v>1554</v>
       </c>
       <c r="D750" s="2"/>
       <c r="E750" t="s" s="2">
-        <v>1562</v>
+        <v>1555</v>
       </c>
       <c r="F750" s="2"/>
       <c r="G750" t="s" s="2">
@@ -84798,10 +84741,10 @@
         <v>230</v>
       </c>
       <c r="N750" t="s" s="2">
-        <v>1563</v>
+        <v>1556</v>
       </c>
       <c r="O750" t="s" s="2">
-        <v>1564</v>
+        <v>1557</v>
       </c>
       <c r="P750" s="2"/>
       <c r="Q750" t="s" s="2">
@@ -84851,7 +84794,7 @@
         <v>73</v>
       </c>
       <c r="AG750" t="s" s="2">
-        <v>1561</v>
+        <v>1554</v>
       </c>
       <c r="AH750" t="s" s="2">
         <v>74</v>
@@ -84860,7 +84803,7 @@
         <v>81</v>
       </c>
       <c r="AJ750" t="s" s="2">
-        <v>727</v>
+        <v>73</v>
       </c>
       <c r="AK750" t="s" s="2">
         <v>93</v>
@@ -84871,10 +84814,10 @@
         <v>1383</v>
       </c>
       <c r="B751" t="s" s="2">
-        <v>1565</v>
+        <v>1558</v>
       </c>
       <c r="C751" t="s" s="2">
-        <v>1565</v>
+        <v>1558</v>
       </c>
       <c r="D751" s="2"/>
       <c r="E751" t="s" s="2">
@@ -84974,10 +84917,10 @@
         <v>1383</v>
       </c>
       <c r="B752" t="s" s="2">
-        <v>1566</v>
+        <v>1559</v>
       </c>
       <c r="C752" t="s" s="2">
-        <v>1566</v>
+        <v>1559</v>
       </c>
       <c r="D752" s="2"/>
       <c r="E752" t="s" s="2">
@@ -85068,7 +85011,7 @@
         <v>75</v>
       </c>
       <c r="AJ752" t="s" s="2">
-        <v>727</v>
+        <v>73</v>
       </c>
       <c r="AK752" t="s" s="2">
         <v>130</v>
@@ -85079,10 +85022,10 @@
         <v>1383</v>
       </c>
       <c r="B753" t="s" s="2">
-        <v>1567</v>
+        <v>1560</v>
       </c>
       <c r="C753" t="s" s="2">
-        <v>1567</v>
+        <v>1560</v>
       </c>
       <c r="D753" s="2"/>
       <c r="E753" t="s" s="2">
@@ -85175,7 +85118,7 @@
         <v>75</v>
       </c>
       <c r="AJ753" t="s" s="2">
-        <v>727</v>
+        <v>73</v>
       </c>
       <c r="AK753" t="s" s="2">
         <v>93</v>
@@ -85186,10 +85129,10 @@
         <v>1383</v>
       </c>
       <c r="B754" t="s" s="2">
-        <v>1568</v>
+        <v>1561</v>
       </c>
       <c r="C754" t="s" s="2">
-        <v>1568</v>
+        <v>1561</v>
       </c>
       <c r="D754" s="2"/>
       <c r="E754" t="s" s="2">
@@ -85289,10 +85232,10 @@
         <v>1383</v>
       </c>
       <c r="B755" t="s" s="2">
-        <v>1569</v>
+        <v>1562</v>
       </c>
       <c r="C755" t="s" s="2">
-        <v>1569</v>
+        <v>1562</v>
       </c>
       <c r="D755" s="2"/>
       <c r="E755" t="s" s="2">
@@ -85383,7 +85326,7 @@
         <v>75</v>
       </c>
       <c r="AJ755" t="s" s="2">
-        <v>727</v>
+        <v>73</v>
       </c>
       <c r="AK755" t="s" s="2">
         <v>130</v>
@@ -85394,10 +85337,10 @@
         <v>1383</v>
       </c>
       <c r="B756" t="s" s="2">
-        <v>1570</v>
+        <v>1563</v>
       </c>
       <c r="C756" t="s" s="2">
-        <v>1570</v>
+        <v>1563</v>
       </c>
       <c r="D756" s="2"/>
       <c r="E756" t="s" s="2">
@@ -85490,7 +85433,7 @@
         <v>81</v>
       </c>
       <c r="AJ756" t="s" s="2">
-        <v>727</v>
+        <v>73</v>
       </c>
       <c r="AK756" t="s" s="2">
         <v>93</v>
@@ -85501,10 +85444,10 @@
         <v>1383</v>
       </c>
       <c r="B757" t="s" s="2">
-        <v>1571</v>
+        <v>1564</v>
       </c>
       <c r="C757" t="s" s="2">
-        <v>1571</v>
+        <v>1564</v>
       </c>
       <c r="D757" s="2"/>
       <c r="E757" t="s" s="2">
@@ -85595,7 +85538,7 @@
         <v>81</v>
       </c>
       <c r="AJ757" t="s" s="2">
-        <v>727</v>
+        <v>73</v>
       </c>
       <c r="AK757" t="s" s="2">
         <v>93</v>
@@ -85606,10 +85549,10 @@
         <v>1383</v>
       </c>
       <c r="B758" t="s" s="2">
-        <v>1572</v>
+        <v>1565</v>
       </c>
       <c r="C758" t="s" s="2">
-        <v>1572</v>
+        <v>1565</v>
       </c>
       <c r="D758" s="2"/>
       <c r="E758" t="s" s="2">
@@ -85640,9 +85583,7 @@
       <c r="N758" t="s" s="2">
         <v>191</v>
       </c>
-      <c r="O758" t="s" s="2">
-        <v>1456</v>
-      </c>
+      <c r="O758" s="2"/>
       <c r="P758" t="s" s="2">
         <v>192</v>
       </c>
@@ -85702,7 +85643,7 @@
         <v>81</v>
       </c>
       <c r="AJ758" t="s" s="2">
-        <v>727</v>
+        <v>73</v>
       </c>
       <c r="AK758" t="s" s="2">
         <v>93</v>
@@ -85713,10 +85654,10 @@
         <v>1383</v>
       </c>
       <c r="B759" t="s" s="2">
-        <v>1573</v>
+        <v>1566</v>
       </c>
       <c r="C759" t="s" s="2">
-        <v>1573</v>
+        <v>1566</v>
       </c>
       <c r="D759" s="2"/>
       <c r="E759" t="s" s="2">
@@ -85747,9 +85688,7 @@
       <c r="N759" t="s" s="2">
         <v>196</v>
       </c>
-      <c r="O759" t="s" s="2">
-        <v>1456</v>
-      </c>
+      <c r="O759" s="2"/>
       <c r="P759" t="s" s="2">
         <v>197</v>
       </c>
@@ -85809,7 +85748,7 @@
         <v>81</v>
       </c>
       <c r="AJ759" t="s" s="2">
-        <v>727</v>
+        <v>73</v>
       </c>
       <c r="AK759" t="s" s="2">
         <v>93</v>
@@ -85820,10 +85759,10 @@
         <v>1383</v>
       </c>
       <c r="B760" t="s" s="2">
-        <v>1574</v>
+        <v>1567</v>
       </c>
       <c r="C760" t="s" s="2">
-        <v>1574</v>
+        <v>1567</v>
       </c>
       <c r="D760" s="2"/>
       <c r="E760" t="s" s="2">
@@ -85916,7 +85855,7 @@
         <v>81</v>
       </c>
       <c r="AJ760" t="s" s="2">
-        <v>727</v>
+        <v>73</v>
       </c>
       <c r="AK760" t="s" s="2">
         <v>93</v>
@@ -85927,10 +85866,10 @@
         <v>1383</v>
       </c>
       <c r="B761" t="s" s="2">
-        <v>1575</v>
+        <v>1568</v>
       </c>
       <c r="C761" t="s" s="2">
-        <v>1575</v>
+        <v>1568</v>
       </c>
       <c r="D761" s="2"/>
       <c r="E761" t="s" s="2">
@@ -86023,7 +85962,7 @@
         <v>81</v>
       </c>
       <c r="AJ761" t="s" s="2">
-        <v>727</v>
+        <v>73</v>
       </c>
       <c r="AK761" t="s" s="2">
         <v>93</v>
@@ -86034,14 +85973,14 @@
         <v>1383</v>
       </c>
       <c r="B762" t="s" s="2">
-        <v>1576</v>
+        <v>1569</v>
       </c>
       <c r="C762" t="s" s="2">
-        <v>1576</v>
+        <v>1569</v>
       </c>
       <c r="D762" s="2"/>
       <c r="E762" t="s" s="2">
-        <v>1577</v>
+        <v>1570</v>
       </c>
       <c r="F762" s="2"/>
       <c r="G762" t="s" s="2">
@@ -86063,13 +86002,13 @@
         <v>305</v>
       </c>
       <c r="M762" t="s" s="2">
-        <v>1578</v>
+        <v>1571</v>
       </c>
       <c r="N762" t="s" s="2">
-        <v>1579</v>
+        <v>1572</v>
       </c>
       <c r="O762" t="s" s="2">
-        <v>1580</v>
+        <v>1573</v>
       </c>
       <c r="P762" s="2"/>
       <c r="Q762" t="s" s="2">
@@ -86119,7 +86058,7 @@
         <v>73</v>
       </c>
       <c r="AG762" t="s" s="2">
-        <v>1576</v>
+        <v>1569</v>
       </c>
       <c r="AH762" t="s" s="2">
         <v>74</v>
@@ -86128,10 +86067,10 @@
         <v>75</v>
       </c>
       <c r="AJ762" t="s" s="2">
-        <v>727</v>
+        <v>73</v>
       </c>
       <c r="AK762" t="s" s="2">
-        <v>1420</v>
+        <v>93</v>
       </c>
     </row>
     <row r="763">
@@ -86139,10 +86078,10 @@
         <v>1383</v>
       </c>
       <c r="B763" t="s" s="2">
-        <v>1581</v>
+        <v>1574</v>
       </c>
       <c r="C763" t="s" s="2">
-        <v>1581</v>
+        <v>1574</v>
       </c>
       <c r="D763" s="2"/>
       <c r="E763" t="s" s="2">
@@ -86242,10 +86181,10 @@
         <v>1383</v>
       </c>
       <c r="B764" t="s" s="2">
-        <v>1582</v>
+        <v>1575</v>
       </c>
       <c r="C764" t="s" s="2">
-        <v>1582</v>
+        <v>1575</v>
       </c>
       <c r="D764" s="2"/>
       <c r="E764" t="s" s="2">
@@ -86336,7 +86275,7 @@
         <v>75</v>
       </c>
       <c r="AJ764" t="s" s="2">
-        <v>727</v>
+        <v>73</v>
       </c>
       <c r="AK764" t="s" s="2">
         <v>130</v>
@@ -86347,10 +86286,10 @@
         <v>1383</v>
       </c>
       <c r="B765" t="s" s="2">
-        <v>1583</v>
+        <v>1576</v>
       </c>
       <c r="C765" t="s" s="2">
-        <v>1583</v>
+        <v>1576</v>
       </c>
       <c r="D765" s="2"/>
       <c r="E765" t="s" s="2">
@@ -86441,7 +86380,7 @@
         <v>81</v>
       </c>
       <c r="AJ765" t="s" s="2">
-        <v>1504</v>
+        <v>277</v>
       </c>
       <c r="AK765" t="s" s="2">
         <v>93</v>
@@ -86452,10 +86391,10 @@
         <v>1383</v>
       </c>
       <c r="B766" t="s" s="2">
-        <v>1584</v>
+        <v>1577</v>
       </c>
       <c r="C766" t="s" s="2">
-        <v>1584</v>
+        <v>1577</v>
       </c>
       <c r="D766" s="2"/>
       <c r="E766" t="s" s="2">
@@ -86546,7 +86485,7 @@
         <v>81</v>
       </c>
       <c r="AJ766" t="s" s="2">
-        <v>727</v>
+        <v>73</v>
       </c>
       <c r="AK766" t="s" s="2">
         <v>93</v>
@@ -86557,10 +86496,10 @@
         <v>1383</v>
       </c>
       <c r="B767" t="s" s="2">
-        <v>1585</v>
+        <v>1578</v>
       </c>
       <c r="C767" t="s" s="2">
-        <v>1585</v>
+        <v>1578</v>
       </c>
       <c r="D767" s="2"/>
       <c r="E767" t="s" s="2">
@@ -86651,7 +86590,7 @@
         <v>81</v>
       </c>
       <c r="AJ767" t="s" s="2">
-        <v>727</v>
+        <v>73</v>
       </c>
       <c r="AK767" t="s" s="2">
         <v>93</v>
@@ -86662,10 +86601,10 @@
         <v>1383</v>
       </c>
       <c r="B768" t="s" s="2">
-        <v>1586</v>
+        <v>1579</v>
       </c>
       <c r="C768" t="s" s="2">
-        <v>1586</v>
+        <v>1579</v>
       </c>
       <c r="D768" s="2"/>
       <c r="E768" t="s" s="2">
@@ -86765,10 +86704,10 @@
         <v>1383</v>
       </c>
       <c r="B769" t="s" s="2">
-        <v>1587</v>
+        <v>1580</v>
       </c>
       <c r="C769" t="s" s="2">
-        <v>1587</v>
+        <v>1580</v>
       </c>
       <c r="D769" s="2"/>
       <c r="E769" t="s" s="2">
@@ -86859,7 +86798,7 @@
         <v>75</v>
       </c>
       <c r="AJ769" t="s" s="2">
-        <v>727</v>
+        <v>73</v>
       </c>
       <c r="AK769" t="s" s="2">
         <v>130</v>
@@ -86870,10 +86809,10 @@
         <v>1383</v>
       </c>
       <c r="B770" t="s" s="2">
-        <v>1588</v>
+        <v>1581</v>
       </c>
       <c r="C770" t="s" s="2">
-        <v>1588</v>
+        <v>1581</v>
       </c>
       <c r="D770" s="2"/>
       <c r="E770" t="s" s="2">
@@ -86966,7 +86905,7 @@
         <v>81</v>
       </c>
       <c r="AJ770" t="s" s="2">
-        <v>727</v>
+        <v>73</v>
       </c>
       <c r="AK770" t="s" s="2">
         <v>93</v>
@@ -86977,10 +86916,10 @@
         <v>1383</v>
       </c>
       <c r="B771" t="s" s="2">
-        <v>1589</v>
+        <v>1582</v>
       </c>
       <c r="C771" t="s" s="2">
-        <v>1589</v>
+        <v>1582</v>
       </c>
       <c r="D771" s="2"/>
       <c r="E771" t="s" s="2">
@@ -87073,7 +87012,7 @@
         <v>81</v>
       </c>
       <c r="AJ771" t="s" s="2">
-        <v>727</v>
+        <v>73</v>
       </c>
       <c r="AK771" t="s" s="2">
         <v>93</v>
@@ -87084,10 +87023,10 @@
         <v>1383</v>
       </c>
       <c r="B772" t="s" s="2">
-        <v>1590</v>
+        <v>1583</v>
       </c>
       <c r="C772" t="s" s="2">
-        <v>1590</v>
+        <v>1583</v>
       </c>
       <c r="D772" s="2"/>
       <c r="E772" t="s" s="2">
@@ -87180,7 +87119,7 @@
         <v>81</v>
       </c>
       <c r="AJ772" t="s" s="2">
-        <v>727</v>
+        <v>73</v>
       </c>
       <c r="AK772" t="s" s="2">
         <v>93</v>
@@ -87191,10 +87130,10 @@
         <v>1383</v>
       </c>
       <c r="B773" t="s" s="2">
-        <v>1591</v>
+        <v>1584</v>
       </c>
       <c r="C773" t="s" s="2">
-        <v>1591</v>
+        <v>1584</v>
       </c>
       <c r="D773" s="2"/>
       <c r="E773" t="s" s="2">
@@ -87226,7 +87165,7 @@
         <v>341</v>
       </c>
       <c r="O773" t="s" s="2">
-        <v>1513</v>
+        <v>342</v>
       </c>
       <c r="P773" s="2"/>
       <c r="Q773" t="s" s="2">
@@ -87285,7 +87224,7 @@
         <v>81</v>
       </c>
       <c r="AJ773" t="s" s="2">
-        <v>727</v>
+        <v>73</v>
       </c>
       <c r="AK773" t="s" s="2">
         <v>93</v>
@@ -87296,10 +87235,10 @@
         <v>1383</v>
       </c>
       <c r="B774" t="s" s="2">
-        <v>1592</v>
+        <v>1585</v>
       </c>
       <c r="C774" t="s" s="2">
-        <v>1592</v>
+        <v>1585</v>
       </c>
       <c r="D774" s="2"/>
       <c r="E774" t="s" s="2">
@@ -87330,9 +87269,7 @@
       <c r="N774" t="s" s="2">
         <v>348</v>
       </c>
-      <c r="O774" t="s" s="2">
-        <v>1515</v>
-      </c>
+      <c r="O774" s="2"/>
       <c r="P774" s="2"/>
       <c r="Q774" t="s" s="2">
         <v>73</v>
@@ -87390,10 +87327,10 @@
         <v>81</v>
       </c>
       <c r="AJ774" t="s" s="2">
-        <v>727</v>
+        <v>73</v>
       </c>
       <c r="AK774" t="s" s="2">
-        <v>1516</v>
+        <v>93</v>
       </c>
     </row>
     <row r="775">
@@ -87401,10 +87338,10 @@
         <v>1383</v>
       </c>
       <c r="B775" t="s" s="2">
-        <v>1593</v>
+        <v>1586</v>
       </c>
       <c r="C775" t="s" s="2">
-        <v>1593</v>
+        <v>1586</v>
       </c>
       <c r="D775" s="2"/>
       <c r="E775" t="s" s="2">
@@ -87495,10 +87432,10 @@
         <v>81</v>
       </c>
       <c r="AJ775" t="s" s="2">
-        <v>727</v>
+        <v>73</v>
       </c>
       <c r="AK775" t="s" s="2">
-        <v>1420</v>
+        <v>93</v>
       </c>
     </row>
     <row r="776">
@@ -87506,10 +87443,10 @@
         <v>1383</v>
       </c>
       <c r="B776" t="s" s="2">
-        <v>1594</v>
+        <v>1587</v>
       </c>
       <c r="C776" t="s" s="2">
-        <v>1594</v>
+        <v>1587</v>
       </c>
       <c r="D776" s="2"/>
       <c r="E776" t="s" s="2">
@@ -87600,7 +87537,7 @@
         <v>81</v>
       </c>
       <c r="AJ776" t="s" s="2">
-        <v>727</v>
+        <v>73</v>
       </c>
       <c r="AK776" t="s" s="2">
         <v>93</v>
@@ -87611,10 +87548,10 @@
         <v>1383</v>
       </c>
       <c r="B777" t="s" s="2">
-        <v>1595</v>
+        <v>1588</v>
       </c>
       <c r="C777" t="s" s="2">
-        <v>1595</v>
+        <v>1588</v>
       </c>
       <c r="D777" s="2"/>
       <c r="E777" t="s" s="2">
@@ -87640,14 +87577,12 @@
         <v>148</v>
       </c>
       <c r="M777" t="s" s="2">
-        <v>1596</v>
+        <v>1589</v>
       </c>
       <c r="N777" t="s" s="2">
-        <v>1597</v>
-      </c>
-      <c r="O777" t="s" s="2">
-        <v>1598</v>
-      </c>
+        <v>1590</v>
+      </c>
+      <c r="O777" s="2"/>
       <c r="P777" s="2"/>
       <c r="Q777" t="s" s="2">
         <v>73</v>
@@ -87675,10 +87610,10 @@
         <v>151</v>
       </c>
       <c r="Z777" t="s" s="2">
-        <v>1599</v>
+        <v>1591</v>
       </c>
       <c r="AA777" t="s" s="2">
-        <v>1600</v>
+        <v>1592</v>
       </c>
       <c r="AB777" t="s" s="2">
         <v>73</v>
@@ -87696,7 +87631,7 @@
         <v>73</v>
       </c>
       <c r="AG777" t="s" s="2">
-        <v>1595</v>
+        <v>1588</v>
       </c>
       <c r="AH777" t="s" s="2">
         <v>74</v>
@@ -87705,7 +87640,7 @@
         <v>75</v>
       </c>
       <c r="AJ777" t="s" s="2">
-        <v>727</v>
+        <v>73</v>
       </c>
       <c r="AK777" t="s" s="2">
         <v>93</v>
@@ -87716,10 +87651,10 @@
         <v>1383</v>
       </c>
       <c r="B778" t="s" s="2">
-        <v>1601</v>
+        <v>1593</v>
       </c>
       <c r="C778" t="s" s="2">
-        <v>1601</v>
+        <v>1593</v>
       </c>
       <c r="D778" s="2"/>
       <c r="E778" t="s" s="2">
@@ -87742,17 +87677,15 @@
         <v>82</v>
       </c>
       <c r="L778" t="s" s="2">
-        <v>1602</v>
+        <v>1594</v>
       </c>
       <c r="M778" t="s" s="2">
-        <v>1596</v>
+        <v>1589</v>
       </c>
       <c r="N778" t="s" s="2">
-        <v>1603</v>
-      </c>
-      <c r="O778" t="s" s="2">
-        <v>1419</v>
-      </c>
+        <v>1595</v>
+      </c>
+      <c r="O778" s="2"/>
       <c r="P778" s="2"/>
       <c r="Q778" t="s" s="2">
         <v>73</v>
@@ -87801,7 +87734,7 @@
         <v>73</v>
       </c>
       <c r="AG778" t="s" s="2">
-        <v>1601</v>
+        <v>1593</v>
       </c>
       <c r="AH778" t="s" s="2">
         <v>74</v>
@@ -87810,10 +87743,10 @@
         <v>75</v>
       </c>
       <c r="AJ778" t="s" s="2">
-        <v>727</v>
+        <v>73</v>
       </c>
       <c r="AK778" t="s" s="2">
-        <v>1420</v>
+        <v>93</v>
       </c>
     </row>
     <row r="779">
@@ -87821,10 +87754,10 @@
         <v>1383</v>
       </c>
       <c r="B779" t="s" s="2">
-        <v>1604</v>
+        <v>1596</v>
       </c>
       <c r="C779" t="s" s="2">
-        <v>1604</v>
+        <v>1596</v>
       </c>
       <c r="D779" s="2"/>
       <c r="E779" t="s" s="2">
@@ -87850,13 +87783,13 @@
         <v>148</v>
       </c>
       <c r="M779" t="s" s="2">
-        <v>1605</v>
+        <v>1597</v>
       </c>
       <c r="N779" t="s" s="2">
-        <v>1606</v>
+        <v>1598</v>
       </c>
       <c r="O779" t="s" s="2">
-        <v>1607</v>
+        <v>1599</v>
       </c>
       <c r="P779" s="2"/>
       <c r="Q779" t="s" s="2">
@@ -87885,10 +87818,10 @@
         <v>151</v>
       </c>
       <c r="Z779" t="s" s="2">
-        <v>1608</v>
+        <v>1600</v>
       </c>
       <c r="AA779" t="s" s="2">
-        <v>1609</v>
+        <v>1601</v>
       </c>
       <c r="AB779" t="s" s="2">
         <v>73</v>
@@ -87906,7 +87839,7 @@
         <v>73</v>
       </c>
       <c r="AG779" t="s" s="2">
-        <v>1604</v>
+        <v>1596</v>
       </c>
       <c r="AH779" t="s" s="2">
         <v>74</v>
@@ -87915,7 +87848,7 @@
         <v>75</v>
       </c>
       <c r="AJ779" t="s" s="2">
-        <v>727</v>
+        <v>73</v>
       </c>
       <c r="AK779" t="s" s="2">
         <v>93</v>
@@ -87926,10 +87859,10 @@
         <v>1383</v>
       </c>
       <c r="B780" t="s" s="2">
-        <v>1610</v>
+        <v>1602</v>
       </c>
       <c r="C780" t="s" s="2">
-        <v>1610</v>
+        <v>1602</v>
       </c>
       <c r="D780" s="2"/>
       <c r="E780" t="s" s="2">
@@ -87958,10 +87891,10 @@
         <v>268</v>
       </c>
       <c r="N780" t="s" s="2">
-        <v>1611</v>
+        <v>1603</v>
       </c>
       <c r="O780" t="s" s="2">
-        <v>1612</v>
+        <v>1604</v>
       </c>
       <c r="P780" s="2"/>
       <c r="Q780" t="s" s="2">
@@ -88011,7 +87944,7 @@
         <v>73</v>
       </c>
       <c r="AG780" t="s" s="2">
-        <v>1610</v>
+        <v>1602</v>
       </c>
       <c r="AH780" t="s" s="2">
         <v>74</v>
@@ -88020,10 +87953,10 @@
         <v>75</v>
       </c>
       <c r="AJ780" t="s" s="2">
-        <v>727</v>
+        <v>73</v>
       </c>
       <c r="AK780" t="s" s="2">
-        <v>1420</v>
+        <v>93</v>
       </c>
     </row>
     <row r="781">
@@ -88031,10 +87964,10 @@
         <v>1383</v>
       </c>
       <c r="B781" t="s" s="2">
-        <v>1613</v>
+        <v>1605</v>
       </c>
       <c r="C781" t="s" s="2">
-        <v>1613</v>
+        <v>1605</v>
       </c>
       <c r="D781" s="2"/>
       <c r="E781" t="s" s="2">
@@ -88134,10 +88067,10 @@
         <v>1383</v>
       </c>
       <c r="B782" t="s" s="2">
-        <v>1614</v>
+        <v>1606</v>
       </c>
       <c r="C782" t="s" s="2">
-        <v>1614</v>
+        <v>1606</v>
       </c>
       <c r="D782" s="2"/>
       <c r="E782" t="s" s="2">
@@ -88228,7 +88161,7 @@
         <v>75</v>
       </c>
       <c r="AJ782" t="s" s="2">
-        <v>727</v>
+        <v>73</v>
       </c>
       <c r="AK782" t="s" s="2">
         <v>130</v>
@@ -88239,10 +88172,10 @@
         <v>1383</v>
       </c>
       <c r="B783" t="s" s="2">
-        <v>1615</v>
+        <v>1607</v>
       </c>
       <c r="C783" t="s" s="2">
-        <v>1615</v>
+        <v>1607</v>
       </c>
       <c r="D783" s="2"/>
       <c r="E783" t="s" s="2">
@@ -88333,7 +88266,7 @@
         <v>81</v>
       </c>
       <c r="AJ783" t="s" s="2">
-        <v>1504</v>
+        <v>277</v>
       </c>
       <c r="AK783" t="s" s="2">
         <v>93</v>
@@ -88344,10 +88277,10 @@
         <v>1383</v>
       </c>
       <c r="B784" t="s" s="2">
-        <v>1616</v>
+        <v>1608</v>
       </c>
       <c r="C784" t="s" s="2">
-        <v>1616</v>
+        <v>1608</v>
       </c>
       <c r="D784" s="2"/>
       <c r="E784" t="s" s="2">
@@ -88438,7 +88371,7 @@
         <v>81</v>
       </c>
       <c r="AJ784" t="s" s="2">
-        <v>727</v>
+        <v>73</v>
       </c>
       <c r="AK784" t="s" s="2">
         <v>93</v>
@@ -88449,10 +88382,10 @@
         <v>1383</v>
       </c>
       <c r="B785" t="s" s="2">
-        <v>1617</v>
+        <v>1609</v>
       </c>
       <c r="C785" t="s" s="2">
-        <v>1617</v>
+        <v>1609</v>
       </c>
       <c r="D785" s="2"/>
       <c r="E785" t="s" s="2">
@@ -88543,7 +88476,7 @@
         <v>81</v>
       </c>
       <c r="AJ785" t="s" s="2">
-        <v>727</v>
+        <v>73</v>
       </c>
       <c r="AK785" t="s" s="2">
         <v>93</v>
@@ -88554,10 +88487,10 @@
         <v>1383</v>
       </c>
       <c r="B786" t="s" s="2">
-        <v>1618</v>
+        <v>1610</v>
       </c>
       <c r="C786" t="s" s="2">
-        <v>1618</v>
+        <v>1610</v>
       </c>
       <c r="D786" s="2"/>
       <c r="E786" t="s" s="2">
@@ -88648,7 +88581,7 @@
         <v>81</v>
       </c>
       <c r="AJ786" t="s" s="2">
-        <v>727</v>
+        <v>73</v>
       </c>
       <c r="AK786" t="s" s="2">
         <v>93</v>
@@ -88659,10 +88592,10 @@
         <v>1383</v>
       </c>
       <c r="B787" t="s" s="2">
-        <v>1619</v>
+        <v>1611</v>
       </c>
       <c r="C787" t="s" s="2">
-        <v>1619</v>
+        <v>1611</v>
       </c>
       <c r="D787" s="2"/>
       <c r="E787" t="s" s="2">
@@ -88685,17 +88618,15 @@
         <v>73</v>
       </c>
       <c r="L787" t="s" s="2">
-        <v>1620</v>
+        <v>1612</v>
       </c>
       <c r="M787" t="s" s="2">
-        <v>1621</v>
+        <v>1613</v>
       </c>
       <c r="N787" t="s" s="2">
-        <v>1622</v>
-      </c>
-      <c r="O787" t="s" s="2">
-        <v>1419</v>
-      </c>
+        <v>1614</v>
+      </c>
+      <c r="O787" s="2"/>
       <c r="P787" s="2"/>
       <c r="Q787" t="s" s="2">
         <v>73</v>
@@ -88744,7 +88675,7 @@
         <v>73</v>
       </c>
       <c r="AG787" t="s" s="2">
-        <v>1619</v>
+        <v>1611</v>
       </c>
       <c r="AH787" t="s" s="2">
         <v>74</v>
@@ -88753,10 +88684,10 @@
         <v>75</v>
       </c>
       <c r="AJ787" t="s" s="2">
-        <v>727</v>
+        <v>73</v>
       </c>
       <c r="AK787" t="s" s="2">
-        <v>1420</v>
+        <v>93</v>
       </c>
     </row>
     <row r="788">
@@ -88764,14 +88695,14 @@
         <v>1383</v>
       </c>
       <c r="B788" t="s" s="2">
-        <v>1623</v>
+        <v>1615</v>
       </c>
       <c r="C788" t="s" s="2">
-        <v>1623</v>
+        <v>1615</v>
       </c>
       <c r="D788" s="2"/>
       <c r="E788" t="s" s="2">
-        <v>1624</v>
+        <v>1616</v>
       </c>
       <c r="F788" s="2"/>
       <c r="G788" t="s" s="2">
@@ -88793,13 +88724,13 @@
         <v>688</v>
       </c>
       <c r="M788" t="s" s="2">
-        <v>1625</v>
+        <v>1617</v>
       </c>
       <c r="N788" t="s" s="2">
-        <v>1626</v>
+        <v>1618</v>
       </c>
       <c r="O788" t="s" s="2">
-        <v>1627</v>
+        <v>1619</v>
       </c>
       <c r="P788" s="2"/>
       <c r="Q788" t="s" s="2">
@@ -88849,7 +88780,7 @@
         <v>73</v>
       </c>
       <c r="AG788" t="s" s="2">
-        <v>1623</v>
+        <v>1615</v>
       </c>
       <c r="AH788" t="s" s="2">
         <v>74</v>
@@ -88858,10 +88789,10 @@
         <v>75</v>
       </c>
       <c r="AJ788" t="s" s="2">
-        <v>727</v>
+        <v>73</v>
       </c>
       <c r="AK788" t="s" s="2">
-        <v>1420</v>
+        <v>93</v>
       </c>
     </row>
     <row r="789">
@@ -88869,10 +88800,10 @@
         <v>1383</v>
       </c>
       <c r="B789" t="s" s="2">
-        <v>1628</v>
+        <v>1620</v>
       </c>
       <c r="C789" t="s" s="2">
-        <v>1628</v>
+        <v>1620</v>
       </c>
       <c r="D789" s="2"/>
       <c r="E789" t="s" s="2">
@@ -88895,16 +88826,16 @@
         <v>82</v>
       </c>
       <c r="L789" t="s" s="2">
-        <v>1629</v>
+        <v>1621</v>
       </c>
       <c r="M789" t="s" s="2">
-        <v>1630</v>
+        <v>1622</v>
       </c>
       <c r="N789" t="s" s="2">
-        <v>1631</v>
+        <v>1623</v>
       </c>
       <c r="O789" t="s" s="2">
-        <v>1632</v>
+        <v>1624</v>
       </c>
       <c r="P789" s="2"/>
       <c r="Q789" t="s" s="2">
@@ -88954,7 +88885,7 @@
         <v>73</v>
       </c>
       <c r="AG789" t="s" s="2">
-        <v>1628</v>
+        <v>1620</v>
       </c>
       <c r="AH789" t="s" s="2">
         <v>74</v>
@@ -88963,10 +88894,10 @@
         <v>75</v>
       </c>
       <c r="AJ789" t="s" s="2">
-        <v>727</v>
+        <v>73</v>
       </c>
       <c r="AK789" t="s" s="2">
-        <v>1420</v>
+        <v>93</v>
       </c>
     </row>
     <row r="790">
@@ -88974,14 +88905,14 @@
         <v>1383</v>
       </c>
       <c r="B790" t="s" s="2">
-        <v>1633</v>
+        <v>1625</v>
       </c>
       <c r="C790" t="s" s="2">
-        <v>1633</v>
+        <v>1625</v>
       </c>
       <c r="D790" s="2"/>
       <c r="E790" t="s" s="2">
-        <v>1634</v>
+        <v>1626</v>
       </c>
       <c r="F790" s="2"/>
       <c r="G790" t="s" s="2">
@@ -89003,16 +88934,16 @@
         <v>148</v>
       </c>
       <c r="M790" t="s" s="2">
-        <v>1635</v>
+        <v>1627</v>
       </c>
       <c r="N790" t="s" s="2">
-        <v>1636</v>
+        <v>1628</v>
       </c>
       <c r="O790" t="s" s="2">
-        <v>1637</v>
+        <v>1629</v>
       </c>
       <c r="P790" t="s" s="2">
-        <v>1638</v>
+        <v>1630</v>
       </c>
       <c r="Q790" t="s" s="2">
         <v>73</v>
@@ -89061,7 +88992,7 @@
         <v>73</v>
       </c>
       <c r="AG790" t="s" s="2">
-        <v>1633</v>
+        <v>1625</v>
       </c>
       <c r="AH790" t="s" s="2">
         <v>74</v>
@@ -89070,7 +89001,7 @@
         <v>75</v>
       </c>
       <c r="AJ790" t="s" s="2">
-        <v>727</v>
+        <v>73</v>
       </c>
       <c r="AK790" t="s" s="2">
         <v>93</v>
@@ -89081,10 +89012,10 @@
         <v>1383</v>
       </c>
       <c r="B791" t="s" s="2">
-        <v>1639</v>
+        <v>1631</v>
       </c>
       <c r="C791" t="s" s="2">
-        <v>1639</v>
+        <v>1631</v>
       </c>
       <c r="D791" s="2"/>
       <c r="E791" t="s" s="2">
@@ -89113,11 +89044,9 @@
         <v>50</v>
       </c>
       <c r="N791" t="s" s="2">
-        <v>1640</v>
-      </c>
-      <c r="O791" t="s" s="2">
-        <v>1641</v>
-      </c>
+        <v>1632</v>
+      </c>
+      <c r="O791" s="2"/>
       <c r="P791" s="2"/>
       <c r="Q791" t="s" s="2">
         <v>73</v>
@@ -89166,7 +89095,7 @@
         <v>73</v>
       </c>
       <c r="AG791" t="s" s="2">
-        <v>1639</v>
+        <v>1631</v>
       </c>
       <c r="AH791" t="s" s="2">
         <v>74</v>
@@ -89175,7 +89104,7 @@
         <v>75</v>
       </c>
       <c r="AJ791" t="s" s="2">
-        <v>727</v>
+        <v>73</v>
       </c>
       <c r="AK791" t="s" s="2">
         <v>93</v>
@@ -89186,10 +89115,10 @@
         <v>1383</v>
       </c>
       <c r="B792" t="s" s="2">
-        <v>1642</v>
+        <v>1633</v>
       </c>
       <c r="C792" t="s" s="2">
-        <v>1642</v>
+        <v>1633</v>
       </c>
       <c r="D792" s="2"/>
       <c r="E792" t="s" s="2">
@@ -89215,14 +89144,12 @@
         <v>159</v>
       </c>
       <c r="M792" t="s" s="2">
-        <v>1643</v>
+        <v>1634</v>
       </c>
       <c r="N792" t="s" s="2">
-        <v>1644</v>
-      </c>
-      <c r="O792" t="s" s="2">
-        <v>1456</v>
-      </c>
+        <v>1635</v>
+      </c>
+      <c r="O792" s="2"/>
       <c r="P792" s="2"/>
       <c r="Q792" t="s" s="2">
         <v>73</v>
@@ -89271,7 +89198,7 @@
         <v>73</v>
       </c>
       <c r="AG792" t="s" s="2">
-        <v>1642</v>
+        <v>1633</v>
       </c>
       <c r="AH792" t="s" s="2">
         <v>74</v>
@@ -89280,7 +89207,7 @@
         <v>81</v>
       </c>
       <c r="AJ792" t="s" s="2">
-        <v>727</v>
+        <v>73</v>
       </c>
       <c r="AK792" t="s" s="2">
         <v>93</v>
@@ -89291,10 +89218,10 @@
         <v>1383</v>
       </c>
       <c r="B793" t="s" s="2">
-        <v>1645</v>
+        <v>1636</v>
       </c>
       <c r="C793" t="s" s="2">
-        <v>1645</v>
+        <v>1636</v>
       </c>
       <c r="D793" s="2"/>
       <c r="E793" t="s" s="2">
@@ -89317,16 +89244,16 @@
         <v>73</v>
       </c>
       <c r="L793" t="s" s="2">
-        <v>1646</v>
+        <v>1637</v>
       </c>
       <c r="M793" t="s" s="2">
-        <v>1647</v>
+        <v>1638</v>
       </c>
       <c r="N793" t="s" s="2">
-        <v>1648</v>
+        <v>1639</v>
       </c>
       <c r="O793" t="s" s="2">
-        <v>1649</v>
+        <v>1640</v>
       </c>
       <c r="P793" s="2"/>
       <c r="Q793" t="s" s="2">
@@ -89376,7 +89303,7 @@
         <v>73</v>
       </c>
       <c r="AG793" t="s" s="2">
-        <v>1645</v>
+        <v>1636</v>
       </c>
       <c r="AH793" t="s" s="2">
         <v>74</v>
@@ -89385,10 +89312,10 @@
         <v>75</v>
       </c>
       <c r="AJ793" t="s" s="2">
-        <v>727</v>
+        <v>73</v>
       </c>
       <c r="AK793" t="s" s="2">
-        <v>1420</v>
+        <v>93</v>
       </c>
     </row>
   </sheetData>

--- a/docs/all-profiles.xlsx
+++ b/docs/all-profiles.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0</t>
+    <t>1.0.0-release</t>
   </si>
   <si>
     <t>Name</t>
@@ -75,7 +75,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>Ministério da Saúde do Brasil (http://www.saude.gov.br)</t>
+    <t>Ministério da Saúde do Brasil (http://www.saude.gov.br, cgiis.datasus@saude.gov.br)</t>
   </si>
   <si>
     <t>Jurisdiction</t>
